--- a/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
@@ -575,46 +575,46 @@
         <v>79</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.06352370510648</v>
+        <v>12.02444258490448</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.922273387522303</v>
+        <v>7.896678142520791</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.262766505510825</v>
+        <v>6.24226892193559</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.661431903117588</v>
+        <v>7.636545766586742</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.124326402709634</v>
+        <v>7.101385727651632</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.156481708734752</v>
+        <v>6.13673517057768</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.073065458968777</v>
+        <v>6.053755497573441</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.142649511335023</v>
+        <v>8.116586050159313</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.083337227205767</v>
+        <v>8.057789345341035</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.695986698598752</v>
+        <v>4.681337143770584</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.760703992449628</v>
+        <v>5.742777209737575</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.988445022535551</v>
+        <v>1.982989678868947</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2979138786359457</v>
+        <v>0.2977380407651466</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.088525403895133</v>
+        <v>3.079118468651345</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.160407833636178</v>
+        <v>6.13915167791464</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.588246764418287</v>
+        <v>3.575883695714595</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.6539689096449024</v>
+        <v>-0.6523951554631324</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.212194069217112</v>
+        <v>6.190967238234208</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.562352671242365</v>
+        <v>8.533548142438121</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.974033453710604</v>
+        <v>5.953968834311212</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.964595228728264</v>
+        <v>3.951401145934121</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.571154447274083</v>
+        <v>1.565751801271603</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.400773322705746</v>
+        <v>4.386290519830659</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.513470751762796</v>
+        <v>4.498742262195385</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.381223633176596</v>
+        <v>2.373709925115612</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.272885236159887</v>
+        <v>6.252907338531564</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.817474264421051</v>
+        <v>6.795580582455329</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.14059021398603</v>
+        <v>5.123909121036938</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.90656167979003</v>
+        <v>1.917745654863666</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.495972283470749</v>
+        <v>3.514061232935646</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.10608647050165</v>
+        <v>11.16092132659578</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.635109707110196</v>
+        <v>5.664131511759784</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.296836317669417</v>
+        <v>4.319281894167851</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.993634651974141</v>
+        <v>3.009225351602865</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.511987197367105</v>
+        <v>4.534433200571122</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.243659554573789</v>
+        <v>3.259894686233132</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.381654388630487</v>
+        <v>2.393550620190155</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0737592948186645</v>
+        <v>-0.07398458711110578</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.324932562119784</v>
+        <v>1.331061708802771</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.161943384211469</v>
+        <v>2.171905693479644</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.741040535031345</v>
+        <v>1.749179819241128</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.247063679894744</v>
+        <v>3.26286693741411</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.844589848804112</v>
+        <v>3.83035718527654</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.529306615405318</v>
+        <v>1.523117835267229</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.067133871588773</v>
+        <v>6.045328493573948</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.789689704207454</v>
+        <v>4.772139168584133</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.777078873976585</v>
+        <v>7.749865099425669</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.551016627960635</v>
+        <v>4.534951423923076</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.467381129868855</v>
+        <v>4.451797021476025</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.000499735224629</v>
+        <v>3.986624206652891</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.64617052302134</v>
+        <v>4.630361452721978</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.206905598755675</v>
+        <v>5.189640349773192</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.884394729306479</v>
+        <v>2.874953791774843</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.8005170328512392</v>
+        <v>0.7980268686906484</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.205417195140356</v>
+        <v>3.194881179876255</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.749812231330509</v>
+        <v>2.740377160040183</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>134</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.000901006777134</v>
+        <v>-0.9996561724079172</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.866619030576992</v>
+        <v>-1.86166221995439</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.96495534128384</v>
+        <v>2.952058857939946</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8556172494763814</v>
+        <v>0.8501606109769213</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.041195474944359</v>
+        <v>7.014358405792187</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.351553632631315</v>
+        <v>4.334905944901671</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.015496844855939</v>
+        <v>4.996807226187215</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.296558978052936</v>
+        <v>5.277150375887217</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.741002684496308</v>
+        <v>3.727048798513245</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.889590379825904</v>
+        <v>2.878903085142326</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.433144074849601</v>
+        <v>3.421079474484564</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.965552111371125</v>
+        <v>4.948597857501134</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.545713611373358</v>
+        <v>4.52975610104572</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.298999893325714</v>
+        <v>3.286940119888662</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1496883202099752</v>
+        <v>-0.1513733838060105</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.013528373478998</v>
+        <v>-7.986331089819856</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.847128936136478</v>
+        <v>-6.826139157941476</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.718640121550791</v>
+        <v>-6.697589664001271</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.259107088680672</v>
+        <v>-7.237181989344954</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.486781152068637</v>
+        <v>-1.483962669951786</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7893399682600375</v>
+        <v>-0.7888410353241824</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.040541006652361</v>
+        <v>-2.035368824803506</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.23477495680541</v>
+        <v>-5.217898201731074</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.955598432891925</v>
+        <v>-2.94633248474787</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.296396254725693</v>
+        <v>-6.274803504376528</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.128652377223354</v>
+        <v>-3.118143389804409</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.687016058137353</v>
+        <v>-6.664273749700889</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.08405731832805</v>
+        <v>-4.070802417424424</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.869378169834036</v>
+        <v>-2.914461535804662</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.23442316470512</v>
+        <v>-5.338849790825584</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.383073540382767</v>
+        <v>-6.497678779233311</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-9.264888020473506</v>
+        <v>-9.440770613435447</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.53664661652531</v>
+        <v>-4.611074343143621</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.832963357951058</v>
+        <v>-3.897092633133909</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.918047186761072</v>
+        <v>-3.984309621538429</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.889495400653011</v>
+        <v>-5.997940352209511</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.443615627154152</v>
+        <v>-4.527303819105775</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.059122040026864</v>
+        <v>-9.237376001056766</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.510428190872162</v>
+        <v>-8.682791369138414</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.791007245901362</v>
+        <v>-5.906966179824273</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.009203833581388</v>
+        <v>-2.048889134316447</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.783630979148199</v>
+        <v>-4.876090878962891</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.972890375004496</v>
+        <v>-8.113924434003238</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.217299554813991</v>
+        <v>-8.376044027072822</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-10.98263802629126</v>
+        <v>-11.18204896706578</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-11.54028114644471</v>
+        <v>-11.7554256703087</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-11.70693315422287</v>
+        <v>-11.91591847930252</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.72573043551264</v>
+        <v>-10.91937687155667</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.441173783663196</v>
+        <v>-9.610881524022048</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.58879373031556</v>
+        <v>-10.78407846301303</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-12.02237349135525</v>
+        <v>-12.24817129208808</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-13.54965266080995</v>
+        <v>-13.80920346058526</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.184083159760867</v>
+        <v>-7.327353345052465</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.526260144292877</v>
+        <v>-8.691571586308434</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.882539656707046</v>
+        <v>-7.01392409935108</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.638585752997415</v>
+        <v>-6.764202767075112</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>135</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-10.27121609798758</v>
+        <v>-10.25080868272634</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.995091835370395</v>
+        <v>-2.987945755526404</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.90793489758267</v>
+        <v>-1.904053795155534</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.519691598622224</v>
+        <v>-2.513943768689124</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.505583121650211</v>
+        <v>-7.490757701183163</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.69051477652097</v>
+        <v>-8.67301302274079</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.295235092447896</v>
+        <v>-7.280631096321841</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.024099396290772</v>
+        <v>-7.009513930492389</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.346063404809769</v>
+        <v>-6.332349196478539</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-10.16986020938759</v>
+        <v>-10.14772304585792</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-11.85943165230227</v>
+        <v>-11.83395785165698</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.3092095077755</v>
+        <v>-13.28105617579303</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-8.534144902209484</v>
+        <v>-8.516125601552744</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.76825602986365</v>
+        <v>-9.747885750757938</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.355876748283023</v>
+        <v>4.437367291295345</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.374682536246262</v>
+        <v>1.388256060093639</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2947109550661082</v>
+        <v>0.2986890841720466</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.596694048743963</v>
+        <v>5.699142462591475</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.319110026722782</v>
+        <v>2.362368377793288</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.930718416486414</v>
+        <v>1.962351546293384</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.537116947942373</v>
+        <v>1.562909336730804</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3944479709299245</v>
+        <v>0.3923086405468794</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3370705492738679</v>
+        <v>0.3292455007903001</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.268694524549353</v>
+        <v>1.269008370873507</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3828989723752088</v>
+        <v>0.3649543472552281</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.641684562442606</v>
+        <v>-1.698564593301448</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.433923634471718</v>
+        <v>-3.517420602847743</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.189482305059897</v>
+        <v>-3.267699270571612</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.225569944252832</v>
+        <v>1.255545633789644</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.3723591805607</v>
+        <v>3.441396460691998</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.323129457323439</v>
+        <v>1.354624076357908</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.758874022966509</v>
+        <v>4.875310032740096</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.223683408139919</v>
+        <v>4.330263349367669</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.091032283941594</v>
+        <v>-2.150751099265797</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.307997406172554</v>
+        <v>-6.472772952131294</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5233486428417109</v>
+        <v>-0.5495586725465103</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9431668748199584</v>
+        <v>-0.9862356511626942</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.198890205061353</v>
+        <v>3.248384926521055</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.827636757306124</v>
+        <v>3.891089229322304</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.862019914651555</v>
+        <v>3.925472386667735</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.789754441169464</v>
+        <v>1.810302521485553</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.099809227083163</v>
+        <v>-2.177264281831192</v>
       </c>
     </row>
     <row r="17">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.03453</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.01451372285339403</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.06746</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3995~4008</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3995</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2229792383736466</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.1004</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3891~3904</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3891</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.3930284841444021</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.1333</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3767~3779</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3767</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.4690932553780058</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.1662</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3625~3637</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3625</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.6375131071222668</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.1992</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3491~3503</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3491</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.6236124566644392</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.2321</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3363~3375</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3363</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6415864683581276</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.265</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3233~3242</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3233</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.5501934096609276</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.298</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3090~3096</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3090</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.200156666463208</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.3309</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2955~2961</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2955</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.259010176919368</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.3638</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2812~2815</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2812</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.04652615581134256</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.3968</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2694~2694</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2694</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.006430153914507741</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.4297</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2523~2523</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2523</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.4593956076536756</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.4626</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2404~2404</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2404</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.7927513636502539</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.4956</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2278~2278</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2278</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.018414181984937</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.5285</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2174~2174</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2174</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.7724310450154164</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.5614</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2069~2069</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2069</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.155667528025894</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.5943</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1976~1976</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1976</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.302108238494476</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.6273</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1880~1880</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1880</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.708689339364497</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.6602</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1756~1756</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1756</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.720684686623741</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.6931</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1638~1638</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1638</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.146366319594662</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.7261</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1516~1516</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1516</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.717643473985277</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.759</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1391~1391</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1391</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.431076417388873</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.7919</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1242~1242</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1242</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.176448958372951</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.8249</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1104~1104</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1104</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.850764578340744</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.8578</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>950~950</t>
-        </is>
+      <c r="B31" t="n">
+        <v>950</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.559193258737388</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.8907</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>765~765</t>
-        </is>
+      <c r="B32" t="n">
+        <v>765</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.493489784365188</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.9237</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>520~520</t>
-        </is>
+      <c r="B33" t="n">
+        <v>520</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1988693720977182</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.9566</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>317~317</t>
-        </is>
+      <c r="B34" t="n">
+        <v>317</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1879496924083242</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.9895</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>12.98275215598051</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.03453</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1124859392575885</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.06746</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>163~163</t>
-        </is>
+      <c r="B7" t="n">
+        <v>163</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5.788770268747079</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.1004</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>267~267</t>
-        </is>
+      <c r="B8" t="n">
+        <v>267</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.933527971924853</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.1333</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>391~392</t>
-        </is>
+      <c r="B9" t="n">
+        <v>391</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.1662</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>533~534</t>
-        </is>
+      <c r="B10" t="n">
+        <v>533</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.435400631100883</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.1992</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>667~668</t>
-        </is>
+      <c r="B11" t="n">
+        <v>667</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.344885033083443</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.2321</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>795~796</t>
-        </is>
+      <c r="B12" t="n">
+        <v>795</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.782943589337762</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.265</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>925~929</t>
-        </is>
+      <c r="B13" t="n">
+        <v>925</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.973730678713601</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.298</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1068~1075</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1068</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.6228407495574686</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.3309</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1203~1210</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1203</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.5926118739289876</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.3638</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1346~1356</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1346</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.05981000162590533</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.3968</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1464~1477</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1464</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.04549194383876909</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.4297</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1635~1648</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1635</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6730499706954092</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.4626</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1754~1767</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1754</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.050314381330523</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.4956</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1880~1893</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1880</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.199196376205748</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.5285</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1984~1997</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1984</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.8159220457983594</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.5614</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2089~2102</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2089</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.113799880628619</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.5943</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2182~2195</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2182</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.149474766679226</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.6273</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2278~2291</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2278</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.380387250807971</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.6602</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2402~2415</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2402</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.23049836161784</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.6931</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2520~2533</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2520</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.368290274414477</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.7261</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2642~2655</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2642</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.53298634280884</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.759</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2767~2780</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2767</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.198474291432994</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.7919</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2916~2929</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2916</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.9058657698514878</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.8249</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3054~3067</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3054</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.009903921775027</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.8578</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3208~3221</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3208</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.7393246909023148</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.8907</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3393~3406</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3393</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.3208017964284196</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.9237</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3638~3651</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3638</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.01466538128912731</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.9566</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3841~3854</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3841</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.002519794003433162</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.9895</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4074~4087</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.2546323500607244</v>

--- a/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>79</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.02444258490448</v>
+        <v>12.03693297230468</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.896678142520791</v>
+        <v>7.909554188459929</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.24226892193559</v>
+        <v>6.255243803996166</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.636545766586742</v>
+        <v>7.649496470319463</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.101385727651632</v>
+        <v>7.114470256460415</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.13673517057768</v>
+        <v>6.149754344746803</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.053755497573441</v>
+        <v>6.066800867140181</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.116586050159313</v>
+        <v>8.129749760696086</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.057789345341035</v>
+        <v>8.070973562145809</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.681337143770584</v>
+        <v>4.694729607416562</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.742777209737575</v>
+        <v>5.756225141988899</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.982989678868947</v>
+        <v>1.996435238732808</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2977380407651466</v>
+        <v>0.3112905974506148</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.079118468651345</v>
+        <v>3.068688832953193</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.13915167791464</v>
+        <v>6.151636005626848</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.575883695714595</v>
+        <v>3.588755030316243</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.6523951554631324</v>
+        <v>-0.6394265704519952</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.190967238234208</v>
+        <v>6.20391588683502</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.533548142438121</v>
+        <v>8.546632479287233</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.953968834311212</v>
+        <v>5.966986945555739</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.951401145934121</v>
+        <v>3.964444690655611</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.565751801271603</v>
+        <v>1.578912253359981</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.386290519830659</v>
+        <v>4.399472962616329</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.498742262195385</v>
+        <v>4.512134137230561</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.373709925115612</v>
+        <v>2.387156800585451</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.252907338531564</v>
+        <v>6.266353155935391</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.795580582455329</v>
+        <v>6.809133404231069</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.123909121036938</v>
+        <v>5.113479485338345</v>
       </c>
     </row>
     <row r="8">
@@ -676,101 +676,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.917745654863666</v>
+        <v>1.911129440948024</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.514061232935646</v>
+        <v>3.496046575640989</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.16092132659578</v>
+        <v>11.08027554165741</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.664131511759784</v>
+        <v>5.627528436009875</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.319281894167851</v>
+        <v>4.294040299372028</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.009225351602865</v>
+        <v>2.995622051662451</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.534433200571122</v>
+        <v>4.509153065342645</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.259894686233132</v>
+        <v>3.245335943253075</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.393550620190155</v>
+        <v>2.386420688307496</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.07398458711110578</v>
+        <v>-0.06021008383901716</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.331061708802771</v>
+        <v>1.334043294513805</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.171905693479644</v>
+        <v>2.168341662533081</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.749179819241128</v>
+        <v>1.748835689615014</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.26286693741411</v>
+        <v>3.575017946877608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.1497</t>
+          <t>X ≈ 0.1498</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.83035718527654</v>
+        <v>3.841648477110674</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.523117835267229</v>
+        <v>1.535466678463784</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.045328493573948</v>
+        <v>6.056480799490103</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.772139168584133</v>
+        <v>4.783620574693394</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.749865099425669</v>
+        <v>7.76067800145043</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.534951423923076</v>
+        <v>4.546626831255395</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.451797021476025</v>
+        <v>4.463539301806229</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.986624206652891</v>
+        <v>3.998626763173789</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.630361452721978</v>
+        <v>4.642224471023901</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.189640349773192</v>
+        <v>5.201591910245838</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.874953791774843</v>
+        <v>2.887612642249145</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.7980268686906484</v>
+        <v>0.8112635227317</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.194881179876255</v>
+        <v>3.207555318859633</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.740377160040183</v>
+        <v>2.72994752434203</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>134</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9996561724079172</v>
+        <v>-0.9870834142621376</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.86166221995439</v>
+        <v>-1.848391323279849</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.952058857939946</v>
+        <v>2.963948267739489</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8501606109769213</v>
+        <v>0.8626441888494512</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.014358405792187</v>
+        <v>7.025200246572894</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.334905944901671</v>
+        <v>4.346530657328394</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.996807226187215</v>
+        <v>5.008289235784851</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.277150375887217</v>
+        <v>5.28869088518568</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.727048798513245</v>
+        <v>3.739064749811327</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.878903085142326</v>
+        <v>2.891401012631263</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.421079474484564</v>
+        <v>3.433518950025977</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.948597857501134</v>
+        <v>4.960629219197614</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.52975610104572</v>
+        <v>4.541978269422899</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.286940119888662</v>
+        <v>3.27651048419051</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1513733838060105</v>
+        <v>-0.139047977571316</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.986331089819856</v>
+        <v>-7.971217445385911</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.826139157941476</v>
+        <v>-6.811438439621512</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.697589664001271</v>
+        <v>-6.682906882935512</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.237181989344954</v>
+        <v>-7.2222900086077</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.483962669951786</v>
+        <v>-1.470722026216244</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7888410353241824</v>
+        <v>-0.7757653829518745</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.035368824803506</v>
+        <v>-2.021785362639548</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.217898201731074</v>
+        <v>-5.203318397513094</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.94633248474787</v>
+        <v>-2.932175053508857</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.274803504376528</v>
+        <v>-6.259562717302472</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.118143389804409</v>
+        <v>-3.103825413437399</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.648827873291154</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.070802417424424</v>
+        <v>-4.081232053122577</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>130</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.914461535804662</v>
+        <v>-2.900932406139709</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.338849790825584</v>
+        <v>-5.323992114476283</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.497678779233311</v>
+        <v>-6.482561338621615</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-9.440770613435447</v>
+        <v>-9.4247219078363</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.611074343143621</v>
+        <v>-4.596465554578621</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.897092633133909</v>
+        <v>-4.298038678462049</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.984309621538429</v>
+        <v>-3.969990069040684</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.997940352209511</v>
+        <v>-5.98284122675112</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.527303819105775</v>
+        <v>-4.512565770151802</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.237376001056766</v>
+        <v>-9.220948264852034</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.682791369138414</v>
+        <v>-8.666395092917071</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.906966179824273</v>
+        <v>-6.325434834948403</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.048889134316447</v>
+        <v>-2.470712215377127</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.876090878962891</v>
+        <v>-4.886520514661044</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>143</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-8.113924434003238</v>
+        <v>-8.098660807911614</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.376044027072822</v>
+        <v>-8.360066463941273</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.18204896706578</v>
+        <v>-11.54581822034379</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-11.7554256703087</v>
+        <v>-11.73851209827095</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-11.91591847930252</v>
+        <v>-12.28112740881409</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.91937687155667</v>
+        <v>-10.90633397526231</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.610881524022048</v>
+        <v>-9.594778365555214</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.78407846301303</v>
+        <v>-10.76740940116999</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-12.24817129208808</v>
+        <v>-12.23094815459572</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-13.80920346058526</v>
+        <v>-13.79117919175973</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.327353345052465</v>
+        <v>-7.709820473240597</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.691571586308434</v>
+        <v>-8.678119297588324</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.01392409935108</v>
+        <v>-7.000368052999477</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.764202767075112</v>
+        <v>-6.774632402773264</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>135</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-10.25080868272634</v>
+        <v>-10.23493309932045</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.987945755526404</v>
+        <v>-2.973883105824513</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.904053795155534</v>
+        <v>-1.891046663737932</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.513943768689124</v>
+        <v>-2.500038119624726</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.490757701183163</v>
+        <v>-7.477646896808224</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.67301302274079</v>
+        <v>-8.659970126446424</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.280631096321841</v>
+        <v>-7.265157991538842</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.009513930492389</v>
+        <v>-6.993922620520877</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.332349196478539</v>
+        <v>-6.316878474282206</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-10.14772304585792</v>
+        <v>-10.13063585870084</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-11.83395785165698</v>
+        <v>-11.82050055794676</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.28105617579303</v>
+        <v>-13.26760388707292</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-8.516125601552744</v>
+        <v>-8.502569555201141</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.747885750757938</v>
+        <v>-9.75831538645609</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>143</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.437367291295345</v>
+        <v>4.448753591630393</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.388256060093639</v>
+        <v>1.401286741923407</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2986890841720466</v>
+        <v>0.3116962155896488</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.699142462591475</v>
+        <v>5.329441731773031</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.362368377793288</v>
+        <v>2.375479182168228</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.962351546293384</v>
+        <v>1.975394442587749</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.562909336730804</v>
+        <v>1.192328704330805</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3923086405468794</v>
+        <v>0.4056467589550579</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3292455007903001</v>
+        <v>0.3427124229976002</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.269008370873507</v>
+        <v>0.8816640450030064</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3649543472552281</v>
+        <v>0.3784116409654459</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.698564593301448</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.517420602847743</v>
+        <v>-3.50386455649614</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.267699270571612</v>
+        <v>-3.278128906269764</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>118</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.255545633789644</v>
+        <v>1.268086555862382</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.441396460691998</v>
+        <v>2.99071691484594</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.354624076357908</v>
+        <v>1.36763120777551</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.875310032740096</v>
+        <v>4.88828917513856</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.330263349367669</v>
+        <v>4.343374153742609</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.150751099265797</v>
+        <v>-2.137708202971432</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.472772952131294</v>
+        <v>-6.459706697830818</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5495586725465103</v>
+        <v>-1.007822888387174</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9862356511626942</v>
+        <v>-1.447227564566226</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.248384926521055</v>
+        <v>3.261790054173886</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.891089229322304</v>
+        <v>3.904546523032522</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.925472386667735</v>
+        <v>3.938924675387845</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.810302521485553</v>
+        <v>1.823858567837156</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.177264281831192</v>
+        <v>-2.187693917529344</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>171</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.879403232490681</v>
+        <v>-7.173708618063827</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8657483007438955</v>
+        <v>0.8786581103199467</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.207482978952115</v>
+        <v>-4.194475847534513</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5684579165200532</v>
+        <v>-0.555478774121589</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.030855739779348</v>
+        <v>-4.017744935404409</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.394232515513849</v>
+        <v>-1.381189619219484</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.478966232786256</v>
+        <v>-1.46589997848578</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.700535596480044</v>
+        <v>-3.687354587184807</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-2.578746100432731</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.272479381140435</v>
+        <v>-2.259074253487604</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.031539224366284</v>
+        <v>1.044996518076502</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.574694311536405</v>
+        <v>4.588146600256515</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6456677707669414</v>
+        <v>0.6592238171185443</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.649775067955517</v>
+        <v>2.639345432257365</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.274950925251801</v>
+        <v>-6.262428635576178</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.844507731493565</v>
+        <v>-2.831597921917513</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.760384841451497</v>
+        <v>-5.747377710033895</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.35282078447425</v>
+        <v>-12.33984164207578</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-7.849225192823731</v>
+        <v>-7.836114388448792</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.03077485174672</v>
+        <v>-5.017731955452355</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.115508569018616</v>
+        <v>-5.102442314718139</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.061683564438965</v>
+        <v>-3.048502555143727</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2386610871934849</v>
+        <v>0.2518598261482481</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.119067373542769</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.704790981209698</v>
+        <v>1.718248274919915</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.98351493707532</v>
+        <v>-4.97006264835521</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.403769548020414</v>
+        <v>-5.390213501668811</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.994384350197713</v>
+        <v>-6.004813985895865</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>126</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.287089113861136</v>
+        <v>-3.274566824185513</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.27961510777741</v>
+        <v>-7.266705298201359</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.087182227072411</v>
+        <v>-6.074175095654809</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.575976713512532</v>
+        <v>-3.562997571114067</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.162523900573795</v>
+        <v>-5.149342891278557</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4616190248507905</v>
+        <v>-0.4484202858960273</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.103799121498241</v>
+        <v>-3.090341827788023</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.863066757803779</v>
+        <v>-3.849614469083669</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.870622956049907</v>
+        <v>-5.857066909698304</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-7.2082032110754</v>
+        <v>-7.218632846773552</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>104</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.160407833636391</v>
+        <v>6.172930123312014</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.220396548558845</v>
+        <v>-1.207486738982794</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.538342178232362</v>
+        <v>-3.52533504681476</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.284218646683044</v>
+        <v>4.297197789081508</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.061894876081858</v>
+        <v>-1.048784071706919</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.004777830865002</v>
+        <v>5.017820727159368</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.996967190515576</v>
+        <v>3.010033444816052</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.529783791733863</v>
+        <v>2.5429648010291</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.507245444013094</v>
+        <v>1.520444182967857</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.541735643600994</v>
+        <v>3.555140771253825</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.470709988409105</v>
+        <v>-1.457252694698887</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.397865292601921</v>
+        <v>-2.384413003881811</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.779658365085503</v>
+        <v>-3.7661023187339</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.529937032809215</v>
+        <v>-3.540366668507367</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>105</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.77915260592448</v>
+        <v>-6.766630316248857</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7382145983246318</v>
+        <v>0.7512217297422339</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.893437030973281</v>
+        <v>-3.880457888574817</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.574715388901936</v>
+        <v>-1.561604584526997</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.579869405956138</v>
+        <v>1.592912302250504</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.219150025601849</v>
+        <v>-4.206083771301373</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.829190567240055</v>
+        <v>-1.816009557944817</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.652095215327343</v>
+        <v>-6.63889647637258</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-7.502220400355483</v>
+        <v>-7.488815272702652</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.849830867529995</v>
+        <v>-4.836373573819778</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.672590567327418</v>
+        <v>-7.659138278607308</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.378559463986605</v>
+        <v>-2.365003417635002</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.033600036472009</v>
+        <v>-4.044029672170161</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>93</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.955803911607582</v>
+        <v>-1.943281621931959</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.492108707367784</v>
+        <v>-2.479198897791733</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.811708596760319</v>
+        <v>-1.798701465342717</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.756724281356625</v>
+        <v>-2.743745138958161</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.144607862020685</v>
+        <v>-1.131497057645745</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.997703558713383</v>
+        <v>-2.984660662419017</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.232974910394503</v>
+        <v>-5.219908656094027</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-7.850695943584114</v>
+        <v>-7.837514934288876</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-12.21277109858387</v>
+        <v>-12.19957235962911</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-9.837089831998895</v>
+        <v>-9.823684704346064</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.66549907029497</v>
+        <v>-4.652041776584753</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.78165354735814</v>
+        <v>-6.76820125863803</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.037814477542838</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.876918008822699</v>
+        <v>-5.887347644520851</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>96</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-6.66010498687676</v>
+        <v>-6.647582697201138</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.188345266507561</v>
+        <v>-6.17543545693151</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.416547306437486</v>
+        <v>-2.403540175019884</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.452960840496424</v>
+        <v>-6.439981698097959</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.03304872223525</v>
+        <v>-8.019937917860311</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.652273451186261</v>
+        <v>-5.639230554891896</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.73700716845854</v>
+        <v>-5.723940914158064</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.120857233907181</v>
+        <v>-4.107676224611943</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.140190453422818</v>
+        <v>-3.126991714468055</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.115315638450511</v>
+        <v>-7.10191051079768</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-10.44506896276809</v>
+        <v>-10.43161166905787</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-10.41068580542266</v>
+        <v>-10.39723351670255</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-8.747607083034218</v>
+        <v>-8.734051036682615</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>124</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.538819744306252</v>
+        <v>1.551342033981875</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8792054815613355</v>
+        <v>-0.8662956719852843</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3388290376484377</v>
+        <v>0.3518361690660399</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.694888621868664</v>
+        <v>3.707867764267128</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8757906577194561</v>
+        <v>-0.8626798533445168</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.99770355871366</v>
+        <v>-2.984660662419294</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6630824372760742</v>
+        <v>-0.6500161829755982</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.289089002652204</v>
+        <v>1.302270011947442</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.191265722239599</v>
+        <v>-1.178066983284836</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.603770383054872</v>
+        <v>3.617175510707703</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.786113832930845</v>
+        <v>1.799571126641062</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.014045377373051</v>
+        <v>1.027497666093161</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.825564072281537</v>
+        <v>-1.812008025929934</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.649963711607469</v>
+        <v>1.639534075909317</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>118</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.188353574447262</v>
+        <v>-4.17583128477164</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.952469560292876</v>
+        <v>-4.939559750716825</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.347338266889366</v>
+        <v>-5.334331135471764</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.217085134281866</v>
+        <v>-5.204105991883402</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.213133467998105</v>
+        <v>-3.200022663623166</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.458064411638375</v>
+        <v>-5.44502151534401</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.69534050179201</v>
+        <v>-4.682274247491534</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.552354409048284</v>
+        <v>-8.539173399753047</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7.765896668111942</v>
+        <v>-7.752697929157179</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-12.85330998873299</v>
+        <v>-12.83990486108016</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.82077517745735</v>
+        <v>-8.807317883747132</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.90156188529411</v>
+        <v>-10.8880058389425</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.804382925898985</v>
+        <v>-9.814812561597137</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>122</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.9524547136526</v>
+        <v>-4.939932423976977</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.105011933174147</v>
+        <v>-4.092102123598096</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.189299638310864</v>
+        <v>-5.1763204959124</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.727720853383033</v>
+        <v>-5.714610049008094</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.069623177962455</v>
+        <v>-7.05658028166809</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.515012632939559</v>
+        <v>-5.501946378639083</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.621540294016143</v>
+        <v>-7.608359284720905</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.862868049050903</v>
+        <v>-6.849669310096139</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.794960447193773</v>
+        <v>-2.781555319540942</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.458730164953877</v>
+        <v>-5.44527287124366</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.604674876460905</v>
+        <v>-4.591222587740795</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.205257356258265</v>
+        <v>-4.191701309906662</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.594880286277061</v>
+        <v>-5.605309921975213</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>125</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.906561679790023</v>
+        <v>5.919083969465646</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.294988066825681</v>
+        <v>8.307897876401732</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.100119360229179</v>
+        <v>7.113126491646781</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8303724928366805</v>
+        <v>0.8433516352351447</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.10804872223558</v>
+        <v>-2.094937917860641</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.810606784519834</v>
+        <v>-5.797563888225469</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.295340501792197</v>
+        <v>-4.282274247491721</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-7.162523900573611</v>
+        <v>-7.149342891278373</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.823523786755914</v>
+        <v>-4.81032504780115</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.473648971783746</v>
+        <v>-2.460243844130915</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.478402296101414</v>
+        <v>-3.464945002391197</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-6.644019138755986</v>
+        <v>-6.630566850035876</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.064273749700888</v>
+        <v>-7.050717703349285</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-5.214552417424599</v>
+        <v>-5.224982053122751</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>149</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.553541545561835</v>
+        <v>4.566063835237458</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.6131088721949</v>
+        <v>3.626018681770951</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1374645323882717</v>
+        <v>-0.1244574009706696</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6783523393780868</v>
+        <v>-0.6653731969796226</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.216773554450178</v>
+        <v>-1.203662750075239</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.261613495929225</v>
+        <v>-2.24857059963486</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.675206273604189</v>
+        <v>-1.662140019303713</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.226737844392837</v>
+        <v>3.239918853688074</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.165737958210535</v>
+        <v>3.178936697165298</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.329035591974552</v>
+        <v>4.342440719627383</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.124282267657051</v>
+        <v>4.137739561367269</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.158665425002404</v>
+        <v>4.172117713722514</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.396128934862794</v>
+        <v>2.409684981214397</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.30356838794453</v>
+        <v>1.293138752246378</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>138</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.218076001369319</v>
+        <v>-3.205553711693696</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.931098889695974</v>
+        <v>-1.918189080119923</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.050605277451986</v>
+        <v>-3.037598146034384</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.644989826003822</v>
+        <v>-3.632010683605358</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1644150458804532</v>
+        <v>0.1775258502553925</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.360407708233794</v>
+        <v>3.373450604528159</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.000311672120937</v>
+        <v>4.013377926421413</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.431678997977109</v>
+        <v>6.444860007272347</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.472128387157049</v>
+        <v>3.485327126111812</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.172727839810364</v>
+        <v>1.186132967463195</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.9679745154927062</v>
+        <v>0.9814318092029239</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.176270716316473</v>
+        <v>3.189723005036583</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.756016105371664</v>
+        <v>2.769572151723267</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.556462075329023</v>
+        <v>1.546032439630871</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>154</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.933949105786738</v>
+        <v>6.946858915362789</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.889729749839574</v>
+        <v>5.902736881257177</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.968034830498937</v>
+        <v>7.981013972897401</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.884159069972306</v>
+        <v>2.897269874347245</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.428354254441139</v>
+        <v>6.441397150735504</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.343620537169002</v>
+        <v>6.356686791469478</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.629683891634187</v>
+        <v>2.642864900929425</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.516735953503904</v>
+        <v>4.529934692458667</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.666610768475898</v>
+        <v>3.680015896128729</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.409909392210274</v>
+        <v>5.423366685920492</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.444292549555705</v>
+        <v>5.457744838275815</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.374687289260081</v>
+        <v>4.388243335611683</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.975057972185859</v>
+        <v>3.964628336487706</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>185</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.96602113924942</v>
+        <v>6.978543428925043</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.354447526285284</v>
+        <v>5.367357335861335</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.797416657526497</v>
+        <v>2.810423788944099</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.765507627971779</v>
+        <v>0.7784867703702432</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.416275602088831</v>
+        <v>9.42938640646377</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.848852674939721</v>
+        <v>4.861895571234086</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.601956795505124</v>
+        <v>2.6150230498056</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.154854591622467</v>
+        <v>3.16805333057723</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.169594271459403</v>
+        <v>7.182999399112234</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.964840947141823</v>
+        <v>6.978298240852041</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.674899780162932</v>
+        <v>2.688352068883042</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.660050574623504</v>
+        <v>7.673606620975107</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.747609744737503</v>
+        <v>5.73718010903935</v>
       </c>
     </row>
     <row r="32">
@@ -1927,98 +1927,98 @@
         <v>245</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.241255557341049</v>
+        <v>4.253777847016671</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.043787443378285</v>
+        <v>-1.030877633802234</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.051139768392424</v>
+        <v>3.064146899810027</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.181392900999967</v>
+        <v>3.194372043398431</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.051134951233891</v>
+        <v>3.06424575560883</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.75674015425566</v>
+        <v>3.769783050550025</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.712822763513991</v>
+        <v>5.725889017814467</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.204823038201901</v>
+        <v>3.218004047497139</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.225455805080792</v>
+        <v>7.238654544035555</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.150840824134526</v>
+        <v>5.164245951787358</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.354250765123069</v>
+        <v>5.367708058833287</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.021286983692974</v>
+        <v>7.034739272413084</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.376542576829721</v>
+        <v>5.390098623181323</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.626263909106008</v>
+        <v>5.615834273407856</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.9402</t>
+          <t>X ≈ 0.9401</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>203</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2159212857013557</v>
+        <v>0.2284435753769785</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.008288559436565</v>
+        <v>5.021198369012616</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.613419852840032</v>
+        <v>4.626426984257634</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.22150549776277</v>
+        <v>6.234484640161234</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.249586745744793</v>
+        <v>1.262697550119732</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.502693708091009</v>
+        <v>4.515736604385374</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.925349153380331</v>
+        <v>3.938415407680807</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.39905245410619</v>
+        <v>7.412233463401428</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.815885080239191</v>
+        <v>8.829083819193954</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.936203244964929</v>
+        <v>9.94960837261776</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.283174058578382</v>
+        <v>6.2966313522886</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.25844391543123</v>
+        <v>10.27189620415134</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>10.82341097936314</v>
+        <v>10.83696702571474</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.08791063676257</v>
+        <v>10.07748100106442</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>233</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.424768792312982</v>
+        <v>-4.412246502637359</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8306103844223429</v>
+        <v>0.8435201939983941</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.280996519599164</v>
+        <v>-1.267989388181562</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.9951793597894749</v>
+        <v>1.008158502187939</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.02757359536108339</v>
+        <v>0.04068439973602267</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.391722664348158</v>
+        <v>-1.378679768053793</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.527835463873132</v>
+        <v>1.540901718173608</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.635759361228963</v>
+        <v>3.648940370524201</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.14557492569044</v>
+        <v>3.158773664645203</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.583003388731179</v>
+        <v>3.59640851638401</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.382541909907168</v>
+        <v>6.395999203617386</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.846109616608814</v>
+        <v>6.859561905328924</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.425855005663912</v>
+        <v>6.439411052015515</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.675576337940214</v>
+        <v>6.665146702242062</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01451372285339403</v>
+        <v>0.014191601559574</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.03106246721734607</v>
+        <v>0.03072635694989856</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05679618444646906</v>
+        <v>-0.05711335172082244</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01115542097331002</v>
+        <v>-0.01148312608676605</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.05153981560432896</v>
+        <v>0.05119332601799442</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.06847209838070256</v>
+        <v>0.06812310663125487</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1196558226381796</v>
+        <v>0.1192936114010621</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1070839425636478</v>
+        <v>0.1067217987485805</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2067287261148891</v>
+        <v>0.2063416188655225</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1794162562691284</v>
+        <v>0.1790304878130939</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2337389842517794</v>
+        <v>0.233338469899131</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3065206060919081</v>
+        <v>0.3061022694147013</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2437017104218029</v>
+        <v>0.2432960356104843</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1882949070722049</v>
+        <v>0.188514879392585</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3995</v>
+        <v>3996</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2229792383736466</v>
+        <v>-0.2234952273415445</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1244778677886558</v>
+        <v>-0.125036255334706</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1813584230958298</v>
+        <v>-0.1819071993938977</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1623865583493398</v>
+        <v>-0.1629389289186278</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08786890205567488</v>
+        <v>-0.08844603271698048</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05152609503694805</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.002310672620687626</v>
+        <v>0.001712762251059985</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05130170612221718</v>
+        <v>-0.05189161691555455</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05147621324408647</v>
+        <v>0.05085965602289377</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.09039203846872113</v>
+        <v>0.08975615586899011</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1247993046989819</v>
+        <v>0.1241522719273789</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2733689022747825</v>
+        <v>0.2726847757770301</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.242633157206015</v>
+        <v>0.2419517987773077</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1311296852036818</v>
+        <v>0.1315745034338036</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3930284841444021</v>
+        <v>-0.3938481688186002</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2233824174171204</v>
+        <v>-0.2242742547457226</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.168768389642679</v>
+        <v>-0.1696816046893659</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3322012062148474</v>
+        <v>-0.3330707122789462</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3183051324919006</v>
+        <v>-0.3191881101189509</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2120430502289921</v>
+        <v>-0.2129485036100789</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1032419897346486</v>
+        <v>-0.1041772995562624</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.09452287414301708</v>
+        <v>-0.0954691098519973</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.064386209753863</v>
+        <v>-0.06534172729819687</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.02743587807395187</v>
+        <v>-0.02841632873060007</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.064689640210851</v>
+        <v>0.06368144176797585</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1135457212491531</v>
+        <v>0.112525086276392</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.06748370148101657</v>
+        <v>0.06646698712079058</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.002319058390931161</v>
+        <v>-0.00154937069726202</v>
       </c>
     </row>
     <row r="9">
@@ -2373,98 +2373,98 @@
         <v>3767</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4690932553780058</v>
+        <v>-0.4703340199523467</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3464094980233625</v>
+        <v>-0.3477253043338209</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.541712781682385</v>
+        <v>-0.5429878545681461</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.529585134281966</v>
+        <v>-0.5308607025991208</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4709626295202582</v>
+        <v>-0.472268426335134</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.3180789625802447</v>
+        <v>-0.319418192861221</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.255902388884607</v>
+        <v>-0.257260998948972</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2049417160561191</v>
+        <v>-0.2063267237724062</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1452952001740968</v>
+        <v>-0.1466983245773932</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02590361369365723</v>
+        <v>-0.02736131960170241</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.02300391244196476</v>
+        <v>0.02152714614990714</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.04578977844145982</v>
+        <v>0.04430712183994956</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.01212656885498831</v>
+        <v>0.01064110769105753</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.109800625547777</v>
+        <v>-0.1202302612459292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.1662</t>
+          <t>X &gt; 0.1663</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3625</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6375131071222668</v>
+        <v>-0.6392447825959238</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.419643396320545</v>
+        <v>-0.4214944799358236</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7997430881889827</v>
+        <v>-0.8015049714995328</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7372664724907878</v>
+        <v>-0.7390417622889274</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7929922950403423</v>
+        <v>-0.794772810540799</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5081838770308451</v>
+        <v>-0.5100329220817841</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.4403143382008068</v>
+        <v>-0.4421861417647648</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3691354708215471</v>
+        <v>-0.371044901743808</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3323691987151349</v>
+        <v>-0.3342919899499108</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2302090599867057</v>
+        <v>-0.2321920392260779</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.08871384834845486</v>
+        <v>-0.09074434086969774</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.01632283587170491</v>
+        <v>0.01426358834294916</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1125496117698503</v>
+        <v>-0.1145897386498973</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2214489691487387</v>
+        <v>-0.2318786048468908</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3491</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6236124566644392</v>
+        <v>-0.6258931994841319</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3642923443678328</v>
+        <v>-0.3667238763815135</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9437538188625112</v>
+        <v>-0.9460396991013695</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.8005215438565472</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.092672900572154</v>
+        <v>-1.094937917860548</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6940830566753533</v>
+        <v>-0.6964492840528465</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6490150800020018</v>
+        <v>-0.6513994618998709</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5858648616720146</v>
+        <v>-0.5882905607093107</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4881875921922472</v>
+        <v>-0.4906454139338692</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3495505172904174</v>
+        <v>-0.3520893376932435</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2234352190902555</v>
+        <v>-0.2260211329006481</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1729996656746593</v>
+        <v>-0.1755997730247145</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2907418104284787</v>
+        <v>-0.2933293871980851</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3561164391948637</v>
+        <v>-0.3665460748930158</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3363</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6415864683581276</v>
+        <v>-0.6444231395390929</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.07418798533783644</v>
+        <v>-0.07728730878336876</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.7198628514518219</v>
+        <v>-0.722795262947173</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5736607218726917</v>
+        <v>-0.5766305764458579</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8588051743268608</v>
+        <v>-0.8617232084892592</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.664019247427845</v>
+        <v>-0.6669794919038949</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6436931286843617</v>
+        <v>-0.6466659388862936</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5306949219512802</v>
+        <v>-0.5337299497527042</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3081688714009942</v>
+        <v>-0.3112751665659985</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.250713737083899</v>
+        <v>-0.253888037775198</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.006887451298283054</v>
+        <v>0.003623030882714318</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.06090379987370653</v>
+        <v>-0.06414783071938501</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.04815718710796801</v>
+        <v>-0.0514311397345395</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.214730829556629</v>
+        <v>-0.2251604652547812</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3233</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5501934096609276</v>
+        <v>-0.5536881551103647</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1375058082635903</v>
+        <v>0.1336844279132308</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4875349607584809</v>
+        <v>-0.491193162780867</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2171112984569277</v>
+        <v>-0.2208458956290471</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.707925189190405</v>
+        <v>-0.7115479826953788</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5340162965643103</v>
+        <v>-0.5209734002699449</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5093658338897313</v>
+        <v>-0.5130339757189333</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.3108551737503689</v>
+        <v>-0.314619381856069</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1385160587806453</v>
+        <v>-0.1423398809284677</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1106429267937727</v>
+        <v>0.1066804217113386</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.356302312621132</v>
+        <v>0.3522473290868504</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1741683032483436</v>
+        <v>0.1876205919684537</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.03229290665544227</v>
+        <v>0.04584895300704517</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.02729599923716819</v>
+        <v>-0.03772563493532033</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3090</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.200156666463208</v>
+        <v>-0.2045195177800778</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5314985676335269</v>
+        <v>0.5267609254974275</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.007389150213022333</v>
+        <v>0.02039628163062446</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3168624734443029</v>
+        <v>0.3121723137488743</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1892381210719449</v>
+        <v>-0.1761273166970057</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.05339928613586409</v>
+        <v>-0.0403563898414987</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.08816300421694478</v>
+        <v>-0.09274612855175235</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1738279752349356</v>
+        <v>0.1691181497820864</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4218984067089906</v>
+        <v>0.41710056668785</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7548299926174593</v>
+        <v>0.7498499766389699</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7118889660345005</v>
+        <v>0.7253462597447182</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5844598256453111</v>
+        <v>0.5979121143654211</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3583799719819609</v>
+        <v>0.3719360183335638</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2844767087889934</v>
+        <v>0.2740470730908413</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2955</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.259010176919368</v>
+        <v>0.25372272706187</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.692285364123066</v>
+        <v>0.6866888254055397</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.09471395482376721</v>
+        <v>0.1077210862413693</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4461886469427867</v>
+        <v>0.4406489325324401</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1443338394407476</v>
+        <v>0.1574446438156869</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3403901739120769</v>
+        <v>0.3534330702064423</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2404269086203286</v>
+        <v>0.2349275098588208</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5020009556996357</v>
+        <v>0.4963636672070919</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7304680941642516</v>
+        <v>0.7247442792194789</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.252916172040187</v>
+        <v>1.246928009725558</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.285049480548324</v>
+        <v>1.298506774258541</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.217909795254165</v>
+        <v>1.231362083974275</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7638142367627268</v>
+        <v>0.7773702831143297</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7428079886667689</v>
+        <v>0.7323783529686168</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2812</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.04652615581134256</v>
+        <v>0.04039078764746762</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6503490309311246</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.08434110863002786</v>
+        <v>0.09734824004762999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1790576385367473</v>
+        <v>0.1920367809352115</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.03153905317317651</v>
+        <v>0.04464985754811579</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2579077854872764</v>
+        <v>0.2709506817816418</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1731740682149976</v>
+        <v>0.1862403225154736</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.5075791922098958</v>
+        <v>0.5009769381459392</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7508716613237496</v>
+        <v>0.7441719305138221</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.252097827647169</v>
+        <v>1.265502955300001</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.331839524666719</v>
+        <v>1.345296818376937</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.36622268201215</v>
+        <v>1.37967497073226</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9815299487343907</v>
+        <v>0.9950859950859936</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9467562596735561</v>
+        <v>0.936326623975404</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2694</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.006430153914507741</v>
+        <v>-0.01338356300188792</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5349286755859737</v>
+        <v>0.5478384851620248</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.02870139437914077</v>
+        <v>0.04170852579674289</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.0266430973637668</v>
+        <v>-0.01366395496530259</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1567495388650428</v>
+        <v>-0.1436387344901036</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3634095480711181</v>
+        <v>0.3764524443654835</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4642734551492467</v>
+        <v>0.4773397094497227</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5538829294189611</v>
+        <v>0.5670639387141989</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8269587670673957</v>
+        <v>0.8401575060221589</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.164658377882091</v>
+        <v>1.178063505534922</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.219741727655077</v>
+        <v>1.233199021365294</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.254124885000508</v>
+        <v>1.267577173720618</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.945228848665856</v>
+        <v>0.9587848950174589</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.083591606331893</v>
+        <v>1.073161970633741</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2523</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4593956076536756</v>
+        <v>0.4719178973292983</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5125068936192676</v>
+        <v>0.5254167031953187</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3158149607047989</v>
+        <v>0.328822092122401</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.0100791912116307</v>
+        <v>0.02305833361009491</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1058236519222575</v>
+        <v>0.1189344562971968</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4825362991107696</v>
+        <v>0.495579195405135</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.595979355520619</v>
+        <v>0.609045609821095</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8422323419947659</v>
+        <v>0.8554133512900037</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.058679938967437</v>
+        <v>1.0718786779222</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.397615396032251</v>
+        <v>1.411020523685082</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.232497426451104</v>
+        <v>1.245954720161322</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.029068455377974</v>
+        <v>1.042520744098084</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9655320370609033</v>
+        <v>0.9790880834125062</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9774412409186439</v>
+        <v>0.9670116052204918</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2404</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7927513636502539</v>
+        <v>0.8052736533258766</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6786819104197761</v>
+        <v>0.6915917199958272</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6165919059862475</v>
+        <v>0.6295990374038496</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6220530252825966</v>
+        <v>0.6350321676810609</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4996051879142556</v>
+        <v>0.5127159922891948</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7554497878595328</v>
+        <v>0.7684926841538982</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8787027594391645</v>
+        <v>0.8917690137396406</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.035479427213403</v>
+        <v>1.048660436508641</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.099271554342266</v>
+        <v>1.112470293297029</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.62185851573696</v>
+        <v>1.635263643389791</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.20911850256747</v>
+        <v>1.222575796277688</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.326696335453668</v>
+        <v>1.340148624173779</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.280817764442212</v>
+        <v>1.294373810793815</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.322552407866581</v>
+        <v>1.312122772168429</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.018414181984937</v>
+        <v>1.03093647166056</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.118868663840694</v>
+        <v>1.131778473416745</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9873888949087188</v>
+        <v>1.000396026326321</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8542530898516034</v>
+        <v>0.8672322322500676</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4036281873343057</v>
+        <v>0.416738991709245</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6571719687725306</v>
+        <v>0.670214865066896</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9236235017197387</v>
+        <v>0.9366897560202148</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.378301384764406</v>
+        <v>1.391482394059643</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.185607029749789</v>
+        <v>1.198805768704553</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.740222845599824</v>
+        <v>1.753627973252655</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.44767320872738</v>
+        <v>1.461130502437598</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.613750834905126</v>
+        <v>1.627203123625236</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.676375943012019</v>
+        <v>1.689931989363622</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.794402806455999</v>
+        <v>1.783973170757847</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2174</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7724310450154164</v>
+        <v>0.7849533346910391</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.230774635363026</v>
+        <v>1.243684444939078</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.203891209355213</v>
+        <v>1.216898340772815</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6901701009323489</v>
+        <v>0.7031492433308131</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4737360063753684</v>
+        <v>0.4868468107503077</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4491908235758402</v>
+        <v>0.4622337198702056</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8244387070395334</v>
+        <v>0.8375049613400094</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.323216669803578</v>
+        <v>1.336397679098816</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.170220463474081</v>
+        <v>1.183419202428844</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.654041920580461</v>
+        <v>1.667447048233292</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.587283076483679</v>
+        <v>1.600740370193897</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.805658874123495</v>
+        <v>1.819111162843605</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.937382184061761</v>
+        <v>1.950938230413364</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.049109036117258</v>
+        <v>2.038679400419106</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>2069</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.155667528025894</v>
+        <v>1.168189817701517</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.380729971127366</v>
+        <v>1.393639780703417</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.227523903486784</v>
+        <v>1.240531034904386</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9227842859734636</v>
+        <v>0.9357634283719278</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5776931820661062</v>
+        <v>0.5908039864410455</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3918098418697298</v>
+        <v>0.4048527381640952</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.080396569256706</v>
+        <v>1.093462823557182</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.483198670716867</v>
+        <v>1.496379680012105</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.567196367908174</v>
+        <v>1.580395106862937</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.118714488825148</v>
+        <v>2.132119616477979</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.913961164507569</v>
+        <v>1.927418458217787</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.286672016391428</v>
+        <v>2.300124305111538</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.156412572193744</v>
+        <v>2.169968618545347</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.357801376678822</v>
+        <v>2.34737174098067</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1976</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.302108238494476</v>
+        <v>1.314630528170099</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.563004261157751</v>
+        <v>1.575914070733802</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.370564704358735</v>
+        <v>1.383571835776337</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.095959537371094</v>
+        <v>1.108938679769558</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.658752897197715</v>
+        <v>0.6718637015726543</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.551336535318228</v>
+        <v>0.5643794316125934</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.377533992135021</v>
+        <v>1.390600246435497</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.922496342341361</v>
+        <v>1.935677351636599</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.215747468304819</v>
+        <v>2.228946207259582</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.681411756961097</v>
+        <v>2.694816884613928</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.223621995396556</v>
+        <v>2.237079289106774</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.713470739786523</v>
+        <v>2.726923028506633</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.495645278639188</v>
+        <v>2.509201324990791</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.745366610915475</v>
+        <v>2.734936975217323</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1880</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.708689339364497</v>
+        <v>1.72121162904012</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.958817854059809</v>
+        <v>1.97172766363586</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.563949147463219</v>
+        <v>1.576956278880822</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.481436322623907</v>
+        <v>1.494415465022371</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.102589575636848</v>
+        <v>1.115700380011788</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8681166197354813</v>
+        <v>0.8811595160298467</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.740829710973848</v>
+        <v>1.753895965274324</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.231093120702987</v>
+        <v>2.244274129998225</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.4892421706909</v>
+        <v>2.502440909645664</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.181670177152327</v>
+        <v>3.195075304805158</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.870533874111345</v>
+        <v>2.883991167821563</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.383640435712095</v>
+        <v>3.397092724432206</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.069768803490604</v>
+        <v>3.083324849842207</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.213107157043481</v>
+        <v>3.202677521345329</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1756</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.720684686623741</v>
+        <v>1.733206976299364</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.159224968875883</v>
+        <v>2.172134778451934</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.650461045878387</v>
+        <v>1.663468177295989</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.325133312882244</v>
+        <v>1.338112455280708</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.242292963413718</v>
+        <v>1.255403767788657</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.141101643726188</v>
+        <v>1.154144540020553</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.910582049460743</v>
+        <v>1.923648303761219</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.297612773686069</v>
+        <v>2.310793782981307</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.749141361307871</v>
+        <v>2.762340100262634</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.15186355668996</v>
+        <v>3.165268684342792</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.947110232372381</v>
+        <v>2.960567526082599</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.550969471722375</v>
+        <v>3.564421760442485</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.415452901779744</v>
+        <v>3.429008948131347</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.323488584853308</v>
+        <v>3.313058949155156</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1638</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.146366319594662</v>
+        <v>2.158888609270285</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.671544843382542</v>
+        <v>2.684454652958593</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.15457601468583</v>
+        <v>2.167583146103432</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.796428658892843</v>
+        <v>1.809407801291307</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.563257749070978</v>
+        <v>1.576368553445917</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.616499442586395</v>
+        <v>1.629542338880761</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.386466580014968</v>
+        <v>2.399532834315444</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.079234341184637</v>
+        <v>3.092415350479875</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.506634943402823</v>
+        <v>3.519833682357586</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.304861406726538</v>
+        <v>4.318266534379369</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.794857777158654</v>
+        <v>3.808315070868872</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.256591361854511</v>
+        <v>4.270043650574621</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.446837361410225</v>
+        <v>4.460393407761828</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.269208266336079</v>
+        <v>4.258778630637927</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1516</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.717643473985277</v>
+        <v>2.730165763660899</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.216887802973517</v>
+        <v>3.229797612549568</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.690092975004902</v>
+        <v>2.703100106422504</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.358604682810295</v>
+        <v>2.371583825208759</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.149998771168207</v>
+        <v>2.163109575543146</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.315514587511828</v>
+        <v>2.328557483806193</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.022337598471736</v>
+        <v>3.035403852772212</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.940378474096576</v>
+        <v>3.953559483391814</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.341120012716381</v>
+        <v>4.354318751671144</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.876219102094794</v>
+        <v>4.889624229747625</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.539539656405175</v>
+        <v>4.552996950115393</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.969701177866703</v>
+        <v>4.983153466586813</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.143114113095947</v>
+        <v>5.15667015944755</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.063020141942154</v>
+        <v>5.052590506244002</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1391</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.431076417388873</v>
+        <v>2.443598707064496</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.760552409025628</v>
+        <v>2.773462218601679</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.293792976332703</v>
+        <v>2.306800107750306</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.495936835036538</v>
+        <v>2.508915977435002</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.53264142873504</v>
+        <v>2.54575223310998</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.045755544739691</v>
+        <v>3.058798441034057</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.679929088430747</v>
+        <v>3.692995342731223</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.938123115961261</v>
+        <v>4.951304125256499</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.164686134164285</v>
+        <v>5.177884873119048</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.536703292774035</v>
+        <v>5.550108420426866</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.013349660668887</v>
+        <v>6.026801949388997</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.240111584590991</v>
+        <v>6.253667630942594</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.986597834192942</v>
+        <v>5.97616819849479</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>1242</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.176448958372951</v>
+        <v>2.188971248048574</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.658273090980352</v>
+        <v>2.671182900556403</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.585465576010172</v>
+        <v>2.598472707427774</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.876749304430881</v>
+        <v>2.889728446829345</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.982450472611532</v>
+        <v>2.995561276986471</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.682468899860204</v>
+        <v>3.69551179615457</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.32237286374734</v>
+        <v>4.335439118047816</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.143434231471481</v>
+        <v>5.156615240766719</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.40449553691559</v>
+        <v>5.417694275870353</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.681584522580089</v>
+        <v>5.69498965023292</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.396315900355901</v>
+        <v>5.409773194066119</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.235852036767362</v>
+        <v>6.249304325487472</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.701265702795091</v>
+        <v>6.714821749146694</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.54841054553836</v>
+        <v>6.537980909840208</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>1104</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.850764578340744</v>
+        <v>2.863286868016367</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.2319445885649</v>
+        <v>3.244854398140951</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.289974432692944</v>
+        <v>3.302981564110546</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.691966695735225</v>
+        <v>3.704945838133689</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.334704900952914</v>
+        <v>3.347815705327854</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.36263051270064</v>
+        <v>4.375696767001116</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.982403635658272</v>
+        <v>4.99558464495351</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.6460414306354</v>
+        <v>5.659240169590163</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.245191607926301</v>
+        <v>6.258596735579133</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.9498585734638</v>
+        <v>5.963315867174018</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.618299701823723</v>
+        <v>6.631751990543833</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.194421902473024</v>
+        <v>7.207977948824627</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.172404104314531</v>
+        <v>7.161974468616378</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>950</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.559193258737388</v>
+        <v>2.57171554841301</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.631830172088932</v>
+        <v>2.644739981664983</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.86854041286076</v>
+        <v>2.881547544278362</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.99879354546826</v>
+        <v>3.011772687866724</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.407740751448721</v>
+        <v>3.42085155582366</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.04150160347104</v>
+        <v>4.054567857771517</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.363791888900074</v>
+        <v>5.376972898195312</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.829107792191458</v>
+        <v>5.842306531146221</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.663193133479318</v>
+        <v>6.676598261132149</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.037387177582794</v>
+        <v>6.050844471293011</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.808612440191382</v>
+        <v>6.822064728911492</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.65151572398333</v>
+        <v>7.665071770334933</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.690710740470124</v>
+        <v>7.680281104771971</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>765</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.493489784365188</v>
+        <v>1.506012074040811</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.973419439374787</v>
+        <v>1.986329248950838</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.885740275261853</v>
+        <v>2.898747406679455</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.538869224862829</v>
+        <v>3.551848367261293</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.954696375803721</v>
+        <v>1.96780718017866</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.905733084761209</v>
+        <v>2.918775981055575</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.389626818469331</v>
+        <v>4.402693072769807</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.491070870668217</v>
+        <v>5.504251879963455</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.475822618472847</v>
+        <v>6.48902135742761</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.540730113183479</v>
+        <v>6.55413524083631</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.813100971872437</v>
+        <v>5.826558265582655</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.808268442943358</v>
+        <v>7.821720731663468</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.649451740495188</v>
+        <v>7.663007786846791</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.160610981268206</v>
+        <v>8.150181345570054</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.9237</t>
+          <t>X &gt; 0.9236</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>520</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1988693720977182</v>
+        <v>0.2113916617733409</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.394988066825761</v>
+        <v>3.407897876401812</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.807811667921484</v>
+        <v>2.820818799339087</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.707295569759758</v>
+        <v>3.720274712158222</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.438105123918355</v>
+        <v>1.451215928293294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.504777830864782</v>
+        <v>2.517820727159148</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.766197959746357</v>
+        <v>3.779264214046833</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.568245330195623</v>
+        <v>6.581426339490861</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.122630059397942</v>
+        <v>6.135828798352705</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.195581797446927</v>
+        <v>7.208986925099758</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.029290011590888</v>
+        <v>6.042747305301106</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.179057784320946</v>
+        <v>8.192510073041056</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.720341634914497</v>
+        <v>8.7338976812661</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.354678351806172</v>
+        <v>9.344248716108019</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>317</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1879496924083242</v>
+        <v>0.2004719820839469</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.361865038434608</v>
+        <v>2.374774848010659</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.651538918588791</v>
+        <v>1.664546050006393</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.097249464445518</v>
+        <v>2.110228606843982</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.558828249373349</v>
+        <v>1.571939053748288</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.225355360590576</v>
+        <v>1.238398256884942</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.664280949311994</v>
+        <v>3.67734720361247</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.036214269773389</v>
+        <v>6.049395279068627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.39792731734503</v>
+        <v>4.411126056299793</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.440546611812373</v>
+        <v>5.453951739465204</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.866708113993219</v>
+        <v>5.880165407703437</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.847463511086282</v>
+        <v>6.860915799806392</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.373581139889019</v>
+        <v>7.387137186240622</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.885132125162158</v>
+        <v>8.874702489464006</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.484631310718264</v>
+        <v>8.497674207012629</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.69461895656925</v>
+        <v>12.70779996586449</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.00358937544868</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that WR-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that WR-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.314388120839723</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.781571519621224</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.413999977232102</v>
+        <v>-6.400801238277339</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.88317278130765</v>
+        <v>-4.869767653654819</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.468878486577609</v>
+        <v>-7.455421192867391</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-11.00592390066075</v>
+        <v>-10.99247161194064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.854749940177079</v>
+        <v>-7.841193893825476</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>163</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.788770268747079</v>
+        <v>5.801292558422702</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.790693588298161</v>
+        <v>4.803603397874213</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.395824881701571</v>
+        <v>4.408832013119174</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.526078014309071</v>
+        <v>4.539057156707536</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.760662934206223</v>
+        <v>2.773773738581163</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.444607939406552</v>
+        <v>2.457650835700917</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.746377289618927</v>
+        <v>1.759443543919403</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.506187755868105</v>
+        <v>2.519368765163343</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6046970721397926</v>
+        <v>0.6178958110945558</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2454281128881348</v>
+        <v>-0.2320229852353037</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.063678369721046</v>
+        <v>-1.050221076010828</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.710276807467643</v>
+        <v>-4.696824518747533</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.903537553381874</v>
+        <v>-3.889981507030271</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.813325423559576</v>
+        <v>-1.823755059257728</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>267</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.933527971924853</v>
+        <v>5.946050261600476</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.321954358960596</v>
+        <v>4.334864168536647</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.428958311540036</v>
+        <v>2.441965442957638</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.180934290589491</v>
+        <v>5.193913432987955</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.017044910723314</v>
+        <v>5.030155715098253</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.816359507614997</v>
+        <v>3.829402403909363</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.608030284724741</v>
+        <v>2.621096539025217</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.14084688594324</v>
+        <v>2.154027895238478</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.079846999760939</v>
+        <v>2.093045738715702</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.604253649939004</v>
+        <v>1.617658777591835</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2759048200034542</v>
+        <v>0.2893621137136719</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4387756930630999</v>
+        <v>-0.4253234043429899</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2645652016099689</v>
+        <v>0.2781212479615718</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8888183690922489</v>
+        <v>0.8783887333940967</v>
       </c>
     </row>
     <row r="9">
@@ -4064,101 +4064,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.058253372948215</v>
+        <v>4.071163182524266</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.193996911249592</v>
+        <v>5.207004042667194</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.324250043857091</v>
+        <v>5.337229186255556</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.785828828784922</v>
+        <v>4.798939633159861</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.552658521602616</v>
+        <v>3.565701417896982</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.212822763514012</v>
+        <v>3.225889017814488</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.490537323916186</v>
+        <v>2.503718333211424</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.174435396917566</v>
+        <v>2.187634135872329</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6093528059393947</v>
+        <v>0.6228100996496124</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3886339224685003</v>
+        <v>0.4020862111886103</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7336854339725889</v>
+        <v>0.7472414803241918</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.641713567230127</v>
+        <v>1.738283252999693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.1662</t>
+          <t>X &lt; 0.1663</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.435400631100883</v>
+        <v>4.447922920776506</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.385624770945611</v>
+        <v>3.398534580521662</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.425212993187984</v>
+        <v>5.438220124605586</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.180934290589491</v>
+        <v>5.193913432987955</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.578842663532299</v>
+        <v>5.591953467907238</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.816359507614997</v>
+        <v>3.829402403909363</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.544359872739726</v>
+        <v>3.557426127040202</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.889910556355225</v>
+        <v>2.903091565650463</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.828910670172924</v>
+        <v>2.842109409127687</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.166051402747996</v>
+        <v>2.179456530400827</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.212234408018425</v>
+        <v>1.225691701728643</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.497553894951885</v>
+        <v>0.511006183671995</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.388160707227946</v>
+        <v>1.401716753579549</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.934415687641064</v>
+        <v>2.001984239012074</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.344885033083443</v>
+        <v>3.357407322759066</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.332113815328761</v>
+        <v>2.345023624904812</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.931257084780079</v>
+        <v>4.944264216197681</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.3130072233756</v>
+        <v>4.325986365774064</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.870394391536962</v>
+        <v>5.883505195911901</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.922327347216694</v>
+        <v>3.935370243511059</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.837593629944415</v>
+        <v>3.850659884244891</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.370410231162914</v>
+        <v>3.383591240458152</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.010009147375825</v>
+        <v>3.023207886330589</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.309584561150288</v>
+        <v>2.322989688803119</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.655729440425532</v>
+        <v>1.669186734135749</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.390711400166161</v>
+        <v>1.404163688886271</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.018360980838033</v>
+        <v>2.031917027189635</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.206137237747804</v>
+        <v>2.257652677416168</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.782943589337762</v>
+        <v>2.795465879013385</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6688574135594436</v>
+        <v>0.6817672231354948</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.037807802440234</v>
+        <v>3.050814933857836</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.539920231530147</v>
+        <v>2.552899373928611</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.760292986307221</v>
+        <v>3.77340379068216</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.052709798394737</v>
+        <v>3.065752694689102</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.093604221825977</v>
+        <v>3.106670476126453</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.500792682340958</v>
+        <v>2.513973691636195</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.686023951937557</v>
+        <v>1.69922269089232</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.464039470427217</v>
+        <v>1.477444598080048</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3798891611850195</v>
+        <v>0.3933464548952372</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6655285999374811</v>
+        <v>0.6789808886575912</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6221584111031362</v>
+        <v>0.6357144574547391</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.195510475657159</v>
+        <v>1.238334529791814</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.973730678713601</v>
+        <v>1.986252968389223</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1760560666510926</v>
+        <v>-0.1631462570750415</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.689570382834134</v>
+        <v>1.702577514251736</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8510398771208472</v>
+        <v>0.8640190195193114</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.573113818130487</v>
+        <v>2.586224622505426</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.070427698238788</v>
+        <v>2.022457640299834</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.093452601656168</v>
+        <v>2.106518855956644</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.302993340805706</v>
+        <v>1.316174350100944</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8109589718647712</v>
+        <v>0.8241577108195344</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.03916621316315627</v>
+        <v>-0.02576108551032519</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8904712616186572</v>
+        <v>-0.8770139679084394</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2569641225747574</v>
+        <v>-0.3038427121048386</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2471733345323699</v>
+        <v>0.1993362340832903</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3422043393321559</v>
+        <v>0.3784736704193605</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6228407495574686</v>
+        <v>0.6353630392330913</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.267802630848649</v>
+        <v>-1.254892821272598</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.03060689675406536</v>
+        <v>-0.06826885719042508</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8314524606083822</v>
+        <v>-0.818473318209918</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6371516505510897</v>
+        <v>0.5985443912642125</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3334230662264375</v>
+        <v>0.2952599701156373</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5285400952228159</v>
+        <v>0.5416063495232919</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3117776319168968</v>
+        <v>-0.298596622621659</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9324790106365128</v>
+        <v>-0.9192802716817496</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.875887777753995</v>
+        <v>-1.862482650101164</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.749924238211598</v>
+        <v>-1.787333062092692</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.384206054643833</v>
+        <v>-1.421976747328124</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7241427861835774</v>
+        <v>-0.762867236059563</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6093089717317142</v>
+        <v>-0.5783964591096549</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5926118739289876</v>
+        <v>-0.5800895842533649</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.46038383400068</v>
+        <v>-1.447474024424629</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2401618639230136</v>
+        <v>-0.2719974752953718</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.019751576642228</v>
+        <v>-1.006772434243764</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2722871328315151</v>
+        <v>-0.3043671982575731</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6752298168313473</v>
+        <v>-0.7068354114042705</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.345713326978526</v>
+        <v>-0.3326470726780499</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.061446850035082</v>
+        <v>-1.048265840739845</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.536696943342484</v>
+        <v>-1.523498204387721</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.801072335495526</v>
+        <v>-2.787667207842695</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.878733971059958</v>
+        <v>-2.909518324677862</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.71704818439914</v>
+        <v>-2.747979785359263</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.597828566976638</v>
+        <v>-1.629970815382478</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.634835044191021</v>
+        <v>-1.607706305614442</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.05981000162590533</v>
+        <v>-0.04728771195028258</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.155159425799603</v>
+        <v>-1.142249616223552</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1825374663390917</v>
+        <v>-0.2095873726600033</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3075891024365944</v>
+        <v>-0.3345081433626405</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.006954973256014796</v>
+        <v>-0.02049183218847617</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3946304531588822</v>
+        <v>-0.4216584928078788</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1431569340644998</v>
+        <v>-0.1704399279650062</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9064173128608033</v>
+        <v>-0.8932363035655655</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.337513424061612</v>
+        <v>-1.324314685106849</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.36994526808013</v>
+        <v>-2.396291216447807</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.534888582239297</v>
+        <v>-2.561241298687492</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.609004301960738</v>
+        <v>-2.635311105039584</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.801615991720197</v>
+        <v>-1.828759246375988</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.808311704200236</v>
+        <v>-1.785041444362548</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.04549194383876909</v>
+        <v>0.05801423351439183</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7852287353422511</v>
+        <v>-0.8084189820951337</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.05920267366913379</v>
+        <v>-0.08307947041284081</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1079844331351865</v>
+        <v>0.08402960133683024</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3533226287488986</v>
+        <v>0.3289426791543733</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5345198279980892</v>
+        <v>-0.5581884639213257</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6504730646745074</v>
+        <v>-0.6741220735785873</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.8768096148593258</v>
+        <v>-0.9005325581716406</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.309296421201111</v>
+        <v>-1.332774027392986</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.918335620285205</v>
+        <v>-1.941795920373345</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.018006931411577</v>
+        <v>-2.041511759884386</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.083036874090233</v>
+        <v>-2.10650413701611</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.510690131953453</v>
+        <v>-1.534755902530726</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.83804968518416</v>
+        <v>-1.817473520699544</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6730499706954092</v>
+        <v>-0.6919530226507788</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6138158190273018</v>
+        <v>-0.6333642595205191</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4901601051414204</v>
+        <v>-0.5099457609336753</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.03766732566342768</v>
+        <v>0.0175922184672217</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1026959241819583</v>
+        <v>-0.1229014436964206</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6239969245076651</v>
+        <v>-0.6437925986877531</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7367534128761548</v>
+        <v>-0.7565286601513961</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.171055283876477</v>
+        <v>-1.190755802362418</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.443035981877863</v>
+        <v>-1.462610239757268</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.955284115163948</v>
+        <v>-1.974877990472471</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.699647717346842</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.387574422812193</v>
+        <v>-1.407612027081051</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.285300644566412</v>
+        <v>-1.305574148065226</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.368680857791574</v>
+        <v>-1.351632419870917</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.050314381330523</v>
+        <v>-1.066888881213089</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7641285809658527</v>
+        <v>-0.7814060285217792</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.845489704926635</v>
+        <v>-0.8628644483305692</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.8155718775127312</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6255756649467727</v>
+        <v>-0.6432372375884441</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9216170001838506</v>
+        <v>-0.939027302859607</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.032648849321923</v>
+        <v>-1.050038152145433</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.298887536937244</v>
+        <v>-1.316293487530508</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.329265685562056</v>
+        <v>-1.346688684164782</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.034968653240043</v>
+        <v>-2.052284776478928</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.4690682038988</v>
+        <v>-1.486788005804165</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.631262874519081</v>
+        <v>-1.648893543262972</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.564558649985791</v>
+        <v>-1.582380573508736</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.682511368393811</v>
+        <v>-1.667147295287997</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.199196376205748</v>
+        <v>-1.21375657963678</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.198035188988179</v>
+        <v>-1.213074125711231</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.194751078692029</v>
+        <v>-1.209917905816219</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9833841209199434</v>
+        <v>-0.9986367307088031</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4347824437812804</v>
+        <v>-0.4504934734161097</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.691115259096108</v>
+        <v>-0.7066162969073062</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9592514715854321</v>
+        <v>-0.9746471288475718</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.557009584560888</v>
+        <v>-1.572236372995384</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.271269144846102</v>
+        <v>-1.286677115669661</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.933521583248812</v>
+        <v>-1.948838008587238</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.578455402845975</v>
+        <v>-1.594032051223472</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.780682263091798</v>
+        <v>-1.796153679563226</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.853003148956603</v>
+        <v>-1.868571050851941</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.052850289765033</v>
+        <v>-2.039017140842049</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8159220457983594</v>
+        <v>-0.8292643788826979</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.19920030992774</v>
+        <v>-1.21278314513048</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.316923246287111</v>
+        <v>-1.33056088310272</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7086445583167844</v>
+        <v>-0.722563151732281</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4675068255972548</v>
+        <v>-0.4816981987030857</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3937393146403139</v>
+        <v>-0.4079000648436235</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7525981612597192</v>
+        <v>-0.76661159688922</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.343428423186673</v>
+        <v>-1.357278601976518</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.125987336278286</v>
+        <v>-1.13997328900718</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.647089615647026</v>
+        <v>-1.661048268464846</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.572815985079785</v>
+        <v>-1.586876591928423</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.813002018917111</v>
+        <v>-1.826943296940762</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.953946293781492</v>
+        <v>-1.967938247155935</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.130278223876218</v>
+        <v>-2.117677267228551</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.113799880628619</v>
+        <v>-1.125709183173441</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.225430781341778</v>
+        <v>-1.237677765843664</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.214166354056545</v>
+        <v>-1.226521295121422</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8679600464677577</v>
+        <v>-0.8804578885743837</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5229200282412165</v>
+        <v>-0.5357192423007575</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2949177048822591</v>
+        <v>-0.3077640788832312</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.9262565323264624</v>
+        <v>-0.9388312336623486</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.367774497232318</v>
+        <v>-1.380258921812725</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.403084436230607</v>
+        <v>-1.415575644459857</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.940825273742753</v>
+        <v>-1.953271542316301</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.737293309485736</v>
+        <v>-1.749894835167126</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.107242476871718</v>
+        <v>-2.119668188468005</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.975278534389879</v>
+        <v>-1.987876957294766</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.225945428434649</v>
+        <v>-2.214455737333282</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.149474766679226</v>
+        <v>-1.160333152574424</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.279123145571681</v>
+        <v>-1.290279800135771</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.239506722762158</v>
+        <v>-1.250775058034172</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9480946604479996</v>
+        <v>-0.9594755421474375</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5493084210031824</v>
+        <v>-0.5609963120211319</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.409693542510702</v>
+        <v>-0.4213886257882251</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.109228121709883</v>
+        <v>-1.120630411875197</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.643328288142165</v>
+        <v>-1.654596431707787</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.862755611172915</v>
+        <v>-1.873944791859657</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.276759676266913</v>
+        <v>-2.287953034803159</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.86192632356137</v>
+        <v>-1.873362202757171</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.306290201027053</v>
+        <v>-2.31752337177501</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.106325971414122</v>
+        <v>-2.117750670382257</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.381555167195458</v>
+        <v>-2.370927999068698</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.380387250807971</v>
+        <v>-1.390165594234183</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.484924596929694</v>
+        <v>-1.494982961660156</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.28887146545889</v>
+        <v>-1.299100582589034</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.179068066603882</v>
+        <v>-1.189326390103439</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8634488096862967</v>
+        <v>-0.8739588968815326</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6298543785705704</v>
+        <v>-0.6404147845962598</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.303655600260377</v>
+        <v>-1.313945288611492</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.74746260460163</v>
+        <v>-1.75765798974664</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.916471662358184</v>
+        <v>-1.926612263212704</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.480309795622581</v>
+        <v>-2.49037963037717</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.223163365807693</v>
+        <v>-2.233393731576129</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.64752791068581</v>
+        <v>-2.657572549290585</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.386081560144063</v>
+        <v>-2.396331738437013</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.551514665010203</v>
+        <v>-2.541699911832723</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.23049836161784</v>
+        <v>-1.239194176229717</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.453810607573573</v>
+        <v>-1.462702537676861</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.205226682041854</v>
+        <v>-1.214296872064907</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9284998123042882</v>
+        <v>-0.9376678425932923</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8640835625507108</v>
+        <v>-0.87337904555541</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7516856226941044</v>
+        <v>-0.7609815572424665</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.270682967545532</v>
+        <v>-1.279784620935615</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.600152355786463</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.879111655472151</v>
+        <v>-1.888065911588527</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.16674955366247</v>
+        <v>-2.175740312764162</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.01644803414716</v>
+        <v>-2.025543506131847</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.458661401651163</v>
+        <v>-2.467573087042119</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.357157644831979</v>
+        <v>-2.366191912999874</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.334619028581976</v>
+        <v>-2.325939190034944</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.368290274414477</v>
+        <v>-1.375943654843745</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.616860274406463</v>
+        <v>-1.624672198608053</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.398339746843121</v>
+        <v>-1.406304787974072</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.128520787795729</v>
+        <v>-1.136577246629734</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9736873145644722</v>
+        <v>-0.9818944395996851</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9713662781907217</v>
+        <v>-0.979533045995332</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.430599702425269</v>
+        <v>-1.438603361415687</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.916284787351131</v>
+        <v>-1.924174707661443</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.154216856062838</v>
+        <v>-2.162027343921494</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.666358955935976</v>
+        <v>-2.674105230269618</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.334684499827134</v>
+        <v>-2.342599519031452</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.635771716075574</v>
+        <v>-2.643567246389424</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.757094059101917</v>
+        <v>-2.764912786616534</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.684393687265874</v>
+        <v>-2.676469558081109</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.53298634280884</v>
+        <v>-1.539650970293394</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.731236499866021</v>
+        <v>-1.738053159379724</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.54096620328383</v>
+        <v>-1.547913448066865</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.315328864629386</v>
+        <v>-1.322347573208127</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.192469695453148</v>
+        <v>-1.199613634300974</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.252116218482101</v>
+        <v>-1.25920100629412</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.618707810210381</v>
+        <v>-1.625670473906723</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.179140214773007</v>
+        <v>-2.18596048282236</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.371238180409108</v>
+        <v>-2.377998763813231</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.672288427566151</v>
+        <v>-2.679057595547704</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.478780367935066</v>
+        <v>-2.485655508815988</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.72662125675901</v>
+        <v>-2.733402388788242</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.82394079472548</v>
+        <v>-2.830747960535362</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.818791630142236</v>
+        <v>-2.811663854106484</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2767</v>
+        <v>2768</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.198474291432994</v>
+        <v>-1.204396792850069</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.280254826301253</v>
+        <v>-1.286346727914733</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.15214845834533</v>
+        <v>-1.158338063948761</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.218745260134156</v>
+        <v>-1.224898904721663</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.233697137221078</v>
+        <v>-1.239914511306715</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.457453631366675</v>
+        <v>-1.463558124536704</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.739320314337164</v>
+        <v>-1.745337310554696</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.403778859102275</v>
+        <v>-2.409616863881112</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.481821045053167</v>
+        <v>-2.487642033015717</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.663327788095636</v>
+        <v>-2.669190453077618</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.523889660722361</v>
+        <v>-2.529831325018407</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.903462981298425</v>
+        <v>-2.909267211046703</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.015429819065055</v>
+        <v>-3.021248580922425</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.927020794728541</v>
+        <v>-2.920646793007144</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9058657698514878</v>
+        <v>-0.9109501602271877</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.031241441370959</v>
+        <v>-1.036451730972715</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.100495603897919</v>
+        <v>-1.105725967369608</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.191226960341723</v>
+        <v>-1.196416044983515</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.232835047021815</v>
+        <v>-1.23806847151743</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.49843168192065</v>
+        <v>-1.503546794208368</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.736052099465731</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.116664899889152</v>
+        <v>-2.121631635719012</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.193739466317702</v>
+        <v>-2.198689181955842</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.3065256841126</v>
+        <v>-2.311527651046454</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.184534533168907</v>
+        <v>-2.189602536637771</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.542853957124741</v>
+        <v>-2.547798778778599</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.739008065779046</v>
+        <v>-2.743932233849634</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.710848713720893</v>
+        <v>-2.705407147397686</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.009903921775027</v>
+        <v>-1.014162445136698</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.071743831412981</v>
+        <v>-1.076125599307339</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.18829825804162</v>
+        <v>-1.192679118268416</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.301742389669847</v>
+        <v>-1.306077402285254</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.169883524716717</v>
+        <v>-1.17431128600677</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.279450677400305</v>
+        <v>-1.283819193481754</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.477437855598048</v>
+        <v>-1.481751713200318</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.731151351554004</v>
+        <v>-1.735425870696858</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.938136405258696</v>
+        <v>-1.942351191591996</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.149515551247539</v>
+        <v>-2.153738450211428</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.042223035388304</v>
+        <v>-2.046501575314679</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.284595054986355</v>
+        <v>-2.28879386999008</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.490787661321185</v>
+        <v>-2.494958541045627</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.518023275315898</v>
+        <v>-2.513361758523736</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.7393246909023148</v>
+        <v>-0.742865130472282</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6888628648512523</v>
+        <v>-0.6925367712231463</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8496787137068296</v>
+        <v>-0.8533331356824121</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.8581296824274602</v>
+        <v>-0.8617741802354928</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9758137206812521</v>
+        <v>-0.9794624672701175</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9103580283009265</v>
+        <v>-0.9140077800501416</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.102805509568157</v>
+        <v>-1.106403600725471</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.522200316255002</v>
+        <v>-1.525703699987545</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.628752544925845</v>
+        <v>-1.632229217060633</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.870660179753955</v>
+        <v>-1.874124952129762</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.684817743002689</v>
+        <v>-1.688357206625327</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.91380107022016</v>
+        <v>-1.917268812041485</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.161313325892841</v>
+        <v>-2.164736394938075</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.206322990990685</v>
+        <v>-2.202482832181651</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3208017964284196</v>
+        <v>-0.3235928723306571</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.360518541103751</v>
+        <v>-0.363388089540635</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6514670087484902</v>
+        <v>-0.6542743894104817</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7698625938515349</v>
+        <v>-0.7726295633547551</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4106942248809915</v>
+        <v>-0.4135979237377185</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5970813508238564</v>
+        <v>-0.5999154461325844</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9012228547332839</v>
+        <v>-0.903973747638652</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.176057292747778</v>
+        <v>-1.178754655984257</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.368314840316827</v>
+        <v>-1.370960528824973</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.378329572313717</v>
+        <v>-1.381020771735486</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.213620199517202</v>
+        <v>-1.216372732741512</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.663754043026977</v>
+        <v>-1.66637368160243</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.625970862252444</v>
+        <v>-1.628626392598179</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.772642603100991</v>
+        <v>-1.769708040158704</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.9237</t>
+          <t>X &lt; 0.9236</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3638</v>
+        <v>3639</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01466538128912731</v>
+        <v>-0.01651296372164524</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4063817961879295</v>
+        <v>-0.4081799105058792</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4028677595296628</v>
+        <v>-0.4046817275312975</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5044959282159525</v>
+        <v>-0.5062784003910608</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1781337236064786</v>
+        <v>-0.1800256371587992</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.304517920010781</v>
+        <v>-0.3063656430924766</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.456657374220093</v>
+        <v>-0.4584673358075975</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.8815140213200365</v>
+        <v>-0.8832249214567014</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7903643028141047</v>
+        <v>-0.7921033134432989</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.939107511047979</v>
+        <v>-0.9408367620557954</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.771673375475217</v>
+        <v>-0.7734568090908169</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.07918397392082</v>
+        <v>-1.080882697330573</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.154518322385691</v>
+        <v>-1.15621220884379</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.274365501536757</v>
+        <v>-1.272467626082353</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.002519794003433162</v>
+        <v>-0.003613825605683019</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1211032905580893</v>
+        <v>-0.1222007224565047</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1385099232599174</v>
+        <v>-0.139611634488702</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1499443079942751</v>
+        <v>-0.1510408881293515</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1028539170406901</v>
+        <v>-0.1039745317270828</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.050980907668702</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2254860319376348</v>
+        <v>-0.2265714675487942</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4445618522242469</v>
+        <v>-0.4456006875361709</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2833261788515955</v>
+        <v>-0.2844087493868059</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3649363579997029</v>
+        <v>-0.3660160750202479</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3991098923553267</v>
+        <v>-0.4001855745628546</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4802928832264541</v>
+        <v>-0.4813472870806237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5216397049325394</v>
+        <v>-0.522692722865294</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6738598894371037</v>
+        <v>-0.6727696637422227</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2546323500607244</v>
+        <v>-0.2548886332740778</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.06683278486292465</v>
+        <v>-0.0671449422916055</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2036750094158677</v>
+        <v>-0.2039562298412321</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.08461281568438039</v>
+        <v>-0.08492253857146181</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0954109558872176</v>
+        <v>-0.09572146340413923</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1275102632067515</v>
+        <v>-0.1278112553574786</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1253821582488612</v>
+        <v>-0.1256843405832555</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2115435084167459</v>
+        <v>-0.2118275764045663</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08746102627540608</v>
+        <v>-0.08777602819330355</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1393674612394591</v>
+        <v>-0.1396750772763937</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01153940672197251</v>
+        <v>-0.01187977433823306</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06148724474224565</v>
+        <v>-0.06181531704593368</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1243964490873921</v>
+        <v>-0.1247118152236695</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2535313079498849</v>
+        <v>-0.2532029120184589</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
+++ b/workspaces/btc_daily_14days/williams_r/wr_21.xlsx
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.05099</t>
+          <t>X ≈ 0.05108</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>79</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.03693297230468</v>
+        <v>12.61007994251899</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.909554188459929</v>
+        <v>8.489515698309738</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.255243803996166</v>
+        <v>6.832108744430862</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.649496470319463</v>
+        <v>8.227570701597386</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.114470256460415</v>
+        <v>7.734515909673497</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.149754344746803</v>
+        <v>6.173695797911066</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.066800867140181</v>
+        <v>6.11475468329126</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.129749760696086</v>
+        <v>8.17895441152492</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.070973562145809</v>
+        <v>8.144163342841487</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.694729607416562</v>
+        <v>4.793987254910846</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.756225141988899</v>
+        <v>5.856067437101636</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.996435238732808</v>
+        <v>2.120070490794411</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3112905974506148</v>
+        <v>0.4599419863386558</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.068688832953193</v>
+        <v>3.240687592519286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.08393</t>
+          <t>X ≈ 0.08402</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.151636005626848</v>
+        <v>6.124187477124089</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.588755030316243</v>
+        <v>3.588521524817111</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.6394265704519952</v>
+        <v>-0.6397279062961303</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.20391588683502</v>
+        <v>6.205070888158581</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.546632479287233</v>
+        <v>8.597316075074289</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.966986945555739</v>
+        <v>5.990928205661724</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.964444690655611</v>
+        <v>4.01238653912197</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.578912253359981</v>
+        <v>1.628088070638867</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.399472962616329</v>
+        <v>4.472647616519346</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.512134137230561</v>
+        <v>4.611387654345201</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.387156800585451</v>
+        <v>2.486989251315833</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.266353155935391</v>
+        <v>6.389991824968675</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.809133404231069</v>
+        <v>6.957787710804119</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.113479485338345</v>
+        <v>5.285478244905882</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>125</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.911129440948024</v>
+        <v>1.88262890237467</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.496046575640989</v>
+        <v>3.495847380321315</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.08027554165741</v>
+        <v>11.08315831536329</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.627528436009875</v>
+        <v>5.628629424848882</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.294040299372028</v>
+        <v>4.34370396027537</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.995622051662451</v>
+        <v>3.019546186016441</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.509153065342645</v>
+        <v>4.55709488976548</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.245335943253075</v>
+        <v>3.294515578778423</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.386420688307496</v>
+        <v>2.459583568976214</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.06021008383901716</v>
+        <v>0.03902443552565416</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.334043294513805</v>
+        <v>1.43386903586773</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.168341662533081</v>
+        <v>2.291971034059159</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.748835689615014</v>
+        <v>1.897484249045959</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>3.575017946877608</v>
+        <v>2.947016706443904</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.841648477110674</v>
+        <v>4.453762202020698</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.535466678463784</v>
+        <v>1.469970348122693</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.056480799490103</v>
+        <v>6.656426086423217</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.783620574693394</v>
+        <v>5.393322405425224</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.76067800145043</v>
+        <v>8.392742347935389</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.546626831255395</v>
+        <v>5.176279064764827</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.463539301806229</v>
+        <v>5.116492724850765</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.998626763173789</v>
+        <v>3.634815289772618</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.642224471023901</v>
+        <v>4.297368231148916</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.201591910245838</v>
+        <v>4.872860232755613</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.887612642249145</v>
+        <v>2.574106070797789</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.8112635227317</v>
+        <v>0.536208278244878</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.207555318859633</v>
+        <v>2.937721567767348</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.72994752434203</v>
+        <v>2.488275447702648</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9870834142621376</v>
+        <v>-1.01917919640718</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.848391323279849</v>
+        <v>-1.861510762887619</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.963948267739489</v>
+        <v>2.245406110290425</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8626441888494512</v>
+        <v>0.8757815708254597</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.025200246572894</v>
+        <v>6.389280367594772</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.346530657328394</v>
+        <v>4.41012564901758</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.008289235784851</v>
+        <v>5.100929559842129</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.28869088518568</v>
+        <v>6.13320416959219</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.739064749811327</v>
+        <v>4.595594766614276</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.891401012631263</v>
+        <v>3.767034714694638</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.433518950025977</v>
+        <v>3.981850577256218</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.960629219197614</v>
+        <v>5.544105031751137</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.541978269422899</v>
+        <v>5.150601759630106</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.27651048419051</v>
+        <v>3.897392646293532</v>
       </c>
     </row>
     <row r="11">
@@ -832,101 +832,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.139047977571316</v>
+        <v>-1.002054734864068</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.971217445385911</v>
+        <v>-8.042061275031479</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.811438439621512</v>
+        <v>-6.111926273955795</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.682906882935512</v>
+        <v>-5.983277613652277</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-7.2222900086077</v>
+        <v>-6.478850982011934</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.470722026216244</v>
+        <v>-0.01257399613913179</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7757653829518745</v>
+        <v>0.3423547646607688</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.021785362639548</v>
+        <v>-0.9058936297809979</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-5.203318397513094</v>
+        <v>-4.394244133502873</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.932175053508857</v>
+        <v>-2.470667754618908</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.259562717302472</v>
+        <v>-5.772523730752539</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.103825413437399</v>
+        <v>-2.617064558412238</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.648827873291154</v>
+        <v>-6.112714356558314</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.081232053122577</v>
+        <v>-3.539804998982625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.2485</t>
+          <t>X ≈ 0.2486</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.900932406139709</v>
+        <v>-3.291847053337861</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.323992114476283</v>
+        <v>-5.662313306626324</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.482561338621615</v>
+        <v>-6.810666083285362</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-9.4247219078363</v>
+        <v>-9.710883908933098</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.596465554578621</v>
+        <v>-5.252343535180593</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.298038678462049</v>
+        <v>-4.978734038566984</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.969990069040684</v>
+        <v>-5.040008111138548</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.98284122675112</v>
+        <v>-6.267069311313875</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.512565770151802</v>
+        <v>-4.791678768852734</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.220948264852034</v>
+        <v>-9.407229937219086</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.666395092917071</v>
+        <v>-8.857557745116402</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.325434834948403</v>
+        <v>-6.860278502304766</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.470712215377127</v>
+        <v>-3.470685151848485</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.886520514661044</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-8.098660807911614</v>
+        <v>-7.977545961166285</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.360066463941273</v>
+        <v>-8.192104311672324</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.54581822034379</v>
+        <v>-11.32585853831436</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-11.73851209827095</v>
+        <v>-11.88388541590717</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-12.28112740881409</v>
+        <v>-12.37311464362288</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-10.90633397526231</v>
+        <v>-11.41591959024478</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.594778365555214</v>
+        <v>-10.10753756475485</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.76740940116999</v>
+        <v>-11.25744133468489</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-12.23094815459572</v>
+        <v>-12.66325292617653</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-13.79117919175973</v>
+        <v>-14.17087373123391</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.709820473240597</v>
+        <v>-8.214312792696852</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-8.678119297588324</v>
+        <v>-9.525263822991427</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-7.000368052999477</v>
+        <v>-7.869336570961408</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.774632402773264</v>
+        <v>-7.622846307254569</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>135</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-10.23493309932045</v>
+        <v>-10.27085695776938</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.973883105824513</v>
+        <v>-2.977428251205495</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.891046663737932</v>
+        <v>-1.89251647951199</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.500038119624726</v>
+        <v>-2.503412771358462</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.477646896808224</v>
+        <v>-7.43408357906668</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-8.659970126446424</v>
+        <v>-8.64188822848088</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-7.265157991538842</v>
+        <v>-7.222041358958862</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.993922620520877</v>
+        <v>-6.947153888980786</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.316878474282206</v>
+        <v>-6.243689698585563</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-10.13063585870084</v>
+        <v>-10.02769570677726</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-11.82050055794676</v>
+        <v>-11.71218649646015</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.26760388707292</v>
+        <v>-13.13460992732855</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-8.502569555201141</v>
+        <v>-8.350920197712064</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.75831538645609</v>
+        <v>-9.586316626889428</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.448753591630393</v>
+        <v>4.331989953412339</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.401286741923407</v>
+        <v>1.385185673008515</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3116962155896488</v>
+        <v>0.3072578107046269</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.329441731773031</v>
+        <v>5.228468733066379</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.375479182168228</v>
+        <v>2.001607238604826</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.975394442587749</v>
+        <v>1.5898757737206</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.192328704330805</v>
+        <v>0.8447506567184746</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4056467589550579</v>
+        <v>-0.3050236162488531</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3427124229976002</v>
+        <v>-0.3418044016795179</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8816640450030064</v>
+        <v>0.204216235663786</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3784116409654459</v>
+        <v>-0.6841774379790451</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-2.67941778394384</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.50386455649614</v>
+        <v>-4.445366166286902</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.278128906269764</v>
+        <v>-4.198188773008148</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.268086555862382</v>
+        <v>1.611964614150239</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.99071691484594</v>
+        <v>3.325481215454047</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.36763120777551</v>
+        <v>1.269836249651263</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.88828917513856</v>
+        <v>4.353714923469042</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.343374153742609</v>
+        <v>3.861356726394789</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.137708202971432</v>
+        <v>-2.529485421761926</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-6.459706697830818</v>
+        <v>-6.755262104679687</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.007822888387174</v>
+        <v>-1.39614414613898</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.447227564566226</v>
+        <v>-2.268402005739432</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.261790054173886</v>
+        <v>1.895173750180057</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.904546523032522</v>
+        <v>2.521513648191323</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.938924675387845</v>
+        <v>2.579680385556216</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.823858567837156</v>
+        <v>0.5181020990169856</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.187693917529344</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>171</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.173708618063827</v>
+        <v>-7.197410916016004</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8786581103199467</v>
+        <v>0.5579537927346649</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.194475847534513</v>
+        <v>-4.51339151118836</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.555478774121589</v>
+        <v>-0.873650576657937</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.017744935404409</v>
+        <v>-4.289263245477215</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.381189619219484</v>
+        <v>-1.678598396297893</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.46589997848578</v>
+        <v>-1.740339449014286</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.687354587184807</v>
+        <v>-3.963813064782791</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.578746100432731</v>
+        <v>-2.833147964928571</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.259074253487604</v>
+        <v>-2.49432966881087</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.044996518076502</v>
+        <v>1.393361193529323</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.588146600256515</v>
+        <v>4.960299860718905</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.6592238171185443</v>
+        <v>0.8079133648963719</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.639345432257365</v>
+        <v>2.811344191824027</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-6.262428635576178</v>
+        <v>-6.285995492593202</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.831597921917513</v>
+        <v>-2.831381384035318</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.747377710033895</v>
+        <v>-5.747531100038216</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.33984164207578</v>
+        <v>-12.34033613445379</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-7.836114388448792</v>
+        <v>-7.78756846868302</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.017731955452355</v>
+        <v>-4.993774546502742</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.102442314718139</v>
+        <v>-5.054430635727819</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.048502555143727</v>
+        <v>-2.999254992750011</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2518598261482481</v>
+        <v>0.3251169359279444</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.119067373542769</v>
+        <v>-3.019720048248196</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.718248274919915</v>
+        <v>1.818156310938591</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.97006264835521</v>
+        <v>-4.846366027326965</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.390213501668811</v>
+        <v>-5.241523953890983</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.004813985895865</v>
+        <v>-5.832815226329203</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>126</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.274566824185513</v>
+        <v>-3.30014974873523</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.266705298201359</v>
+        <v>-7.264391822260393</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.074175095654809</v>
+        <v>-6.07432848565913</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.562997571114067</v>
+        <v>-3.56349206349207</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.149342891278557</v>
+        <v>-5.100095328884841</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.4484202858960273</v>
+        <v>-0.375163176116331</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.090341827788023</v>
+        <v>-2.990433791769348</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.849614469083669</v>
+        <v>-3.725917848055424</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.857066909698304</v>
+        <v>-5.708377361920476</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-7.218632846773552</v>
+        <v>-7.04663408720689</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>104</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>6.172930123312014</v>
+        <v>6.587792917074097</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.207486738982794</v>
+        <v>-0.7783228318032371</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.52533504681476</v>
+        <v>-3.525488436819082</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.297197789081508</v>
+        <v>4.296703296703505</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.048784071706919</v>
+        <v>-1.000238151941147</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.017820727159368</v>
+        <v>5.041778136108981</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.010033444816052</v>
+        <v>3.058045123806373</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.5429648010291</v>
+        <v>2.592212363422817</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.520444182967857</v>
+        <v>1.593701292747554</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.555140771253825</v>
+        <v>3.654488096548398</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.457252694698887</v>
+        <v>-1.357344658680212</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.384413003881811</v>
+        <v>-2.260716382853566</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.7661023187339</v>
+        <v>-3.617412770956072</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.540366668507367</v>
+        <v>-3.368367908940705</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>105</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.766630316248857</v>
+        <v>-6.792167622384838</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7512217297422339</v>
+        <v>0.7510683397379125</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.880457888574817</v>
+        <v>-3.88095238095282</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.561604584526997</v>
+        <v>-1.513058664761225</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.592912302250504</v>
+        <v>1.616869711200117</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.206083771301373</v>
+        <v>-4.158072092311052</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.816009557944817</v>
+        <v>-1.7667619955511</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.63889647637258</v>
+        <v>-6.565639366592883</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-7.488815272702652</v>
+        <v>-7.389467947408079</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.836373573819778</v>
+        <v>-4.736465537801102</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.659138278607308</v>
+        <v>-7.535441657579064</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.365003417635002</v>
+        <v>-2.216313869857174</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.044029672170161</v>
+        <v>-3.872030912603499</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>93</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.943281621931959</v>
+        <v>-1.474321476333863</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.479198897791733</v>
+        <v>-2.480385684236388</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.798701465342717</v>
+        <v>-1.798854855347038</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.743745138958161</v>
+        <v>-2.744239631336164</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.131497057645745</v>
+        <v>-1.082951137879974</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.984660662419017</v>
+        <v>-2.960703253469404</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.219908656094027</v>
+        <v>-5.171896977103707</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-7.837514934288876</v>
+        <v>-7.788267371895159</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-12.19957235962911</v>
+        <v>-12.12631524984941</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-9.823684704346064</v>
+        <v>-9.724337379051491</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.652041776584753</v>
+        <v>-4.552133740566077</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.76820125863803</v>
+        <v>-6.644504637609785</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.037814477542838</v>
+        <v>-4.889124929765011</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.887347644520851</v>
+        <v>-5.715348884954189</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>96</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-6.647582697201138</v>
+        <v>-6.676778491553769</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-6.17543545693151</v>
+        <v>-6.176622243376165</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.403540175019884</v>
+        <v>-2.403693565024206</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.439981698097959</v>
+        <v>-6.440476190475962</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.019937917860311</v>
+        <v>-7.971391998094539</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.639230554891896</v>
+        <v>-5.615273145942282</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.723940914158064</v>
+        <v>-5.675929235167743</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.107676224611943</v>
+        <v>-4.058428662218226</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.126991714468055</v>
+        <v>-3.053734604688358</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.10191051079768</v>
+        <v>-7.002563185503107</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-10.43161166905787</v>
+        <v>-10.3317036330392</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-10.39723351670255</v>
+        <v>-10.2735368956743</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-8.734051036682615</v>
+        <v>-8.585361488904788</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>124</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.551342033981875</v>
+        <v>1.522146239629244</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8662956719852843</v>
+        <v>-0.8674824584299401</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3518361690660399</v>
+        <v>0.3516827790617185</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.707867764267128</v>
+        <v>3.707373271889125</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8626798533445168</v>
+        <v>-0.814133933578745</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.984660662419294</v>
+        <v>-2.960703253469681</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6500161829755982</v>
+        <v>-0.6020045039852775</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.302270011947442</v>
+        <v>1.351517574341159</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.178066983284836</v>
+        <v>-1.10480987350514</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.617175510707703</v>
+        <v>3.716522836002277</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.799571126641062</v>
+        <v>1.899479162659738</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.027497666093161</v>
+        <v>1.151194287121406</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.812008025929934</v>
+        <v>-1.663318478152107</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.639534075909317</v>
+        <v>1.81153283547598</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>118</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.17583128477164</v>
+        <v>-4.205027079124271</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.939559750716825</v>
+        <v>-4.94074653716148</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.334331135471764</v>
+        <v>-5.334484525476086</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.204105991883402</v>
+        <v>-5.204600484261405</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.200022663623166</v>
+        <v>-3.151476743857394</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.44502151534401</v>
+        <v>-5.421064106394397</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.682274247491534</v>
+        <v>-4.634262568501214</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.539173399753047</v>
+        <v>-8.48992583735933</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7.752697929157179</v>
+        <v>-7.679440819377483</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-12.83990486108016</v>
+        <v>-12.74055753578558</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.807317883747132</v>
+        <v>-8.707409847728456</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.8880058389425</v>
+        <v>-10.73931629116468</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-9.814812561597137</v>
+        <v>-9.642813802030474</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>122</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.939932423976977</v>
+        <v>-4.969128218329608</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.092102123598096</v>
+        <v>-4.093288910042752</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.1763204959124</v>
+        <v>-5.176814988290403</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-5.714610049008094</v>
+        <v>-5.666064129242322</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-7.05658028166809</v>
+        <v>-7.032622872718477</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.501946378639083</v>
+        <v>-5.453934699648762</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.608359284720905</v>
+        <v>-7.559111722327188</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6.849669310096139</v>
+        <v>-6.776412200316443</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.781555319540942</v>
+        <v>-2.682207994246369</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.44527287124366</v>
+        <v>-5.345364835224984</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.591222587740795</v>
+        <v>-4.46752596671255</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.191701309906662</v>
+        <v>-4.043011762128835</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.605309921975213</v>
+        <v>-5.43331116240855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.7426</t>
+          <t>X ≈ 0.7425</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>125</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.919083969465646</v>
+        <v>5.889888175113015</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.307897876401732</v>
+        <v>8.306711089957076</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.113126491646781</v>
+        <v>7.11297310164246</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8433516352351447</v>
+        <v>0.8428571428571416</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.094937917860641</v>
+        <v>-2.046391998094869</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.797563888225469</v>
+        <v>-5.773606479275855</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.282274247491721</v>
+        <v>-4.2342625685014</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-7.149342891278373</v>
+        <v>-7.100095328884656</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.81032504780115</v>
+        <v>-4.737067938021454</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.460243844130915</v>
+        <v>-2.360896518836341</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.464945002391197</v>
+        <v>-3.365036966372521</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-6.630566850035876</v>
+        <v>-6.506870229007632</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.050717703349285</v>
+        <v>-6.902028155571458</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-5.224982053122751</v>
+        <v>-5.052983293556089</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>149</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.566063835237458</v>
+        <v>4.536868040884826</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.626018681770951</v>
+        <v>3.624831895326295</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1244574009706696</v>
+        <v>-0.1246107909749909</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6653731969796226</v>
+        <v>-0.6658676893576256</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.203662750075239</v>
+        <v>-1.155116830309467</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.24857059963486</v>
+        <v>-2.224613190685247</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.662140019303713</v>
+        <v>-1.614128340313393</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.239918853688074</v>
+        <v>3.289166416081791</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.178936697165298</v>
+        <v>3.252193806944994</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.342440719627383</v>
+        <v>4.441788044921957</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.137739561367269</v>
+        <v>4.237647597385944</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.172117713722514</v>
+        <v>4.295814334750759</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.409684981214397</v>
+        <v>2.558374528992225</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.293138752246378</v>
+        <v>1.46513751181304</v>
       </c>
     </row>
     <row r="29">
@@ -1771,98 +1771,98 @@
         <v>138</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.205553711693696</v>
+        <v>-3.234749506046327</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.918189080119923</v>
+        <v>-1.919375866564579</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.037598146034384</v>
+        <v>-3.037751536038705</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.632010683605358</v>
+        <v>-3.632505175983361</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1775258502553925</v>
+        <v>0.2260717700211643</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.373450604528159</v>
+        <v>3.397408013477772</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.013377926421413</v>
+        <v>4.061389605411733</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.444860007272347</v>
+        <v>6.494107569666063</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.485327126111812</v>
+        <v>3.558584235891509</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.186132967463195</v>
+        <v>1.285480292757768</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.9814318092029239</v>
+        <v>1.081339845221599</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.189723005036583</v>
+        <v>3.313419626064828</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.769572151723267</v>
+        <v>2.918261699501095</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.546032439630871</v>
+        <v>1.718031199197533</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.8414</t>
+          <t>X ≈ 0.8413</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>154</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.946858915362789</v>
+        <v>6.945672128918133</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.902736881257177</v>
+        <v>5.902583491252855</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.981013972897401</v>
+        <v>7.980519480519398</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.897269874347245</v>
+        <v>2.945815794113017</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.441397150735504</v>
+        <v>6.465354559685117</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.356686791469478</v>
+        <v>6.404698470459799</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.642864900929425</v>
+        <v>2.692112463323141</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.529934692458667</v>
+        <v>4.603191802238364</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.680015896128729</v>
+        <v>3.779363221423303</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.423366685920492</v>
+        <v>5.523274721939167</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.457744838275815</v>
+        <v>5.58144145930406</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.388243335611683</v>
+        <v>4.536932883389511</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.964628336487706</v>
+        <v>4.136627096054369</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>185</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.978543428925043</v>
+        <v>6.949347634572412</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.367357335861335</v>
+        <v>5.36617054941668</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.810423788944099</v>
+        <v>2.810270398939778</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7784867703702432</v>
+        <v>0.7779922779922401</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.42938640646377</v>
+        <v>9.477932326229542</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.861895571234086</v>
+        <v>4.885852980183699</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.6150230498056</v>
+        <v>2.663034728795921</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.16805333057723</v>
+        <v>3.241310440356926</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.182999399112234</v>
+        <v>7.282346724406807</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.978298240852041</v>
+        <v>7.078206276870716</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.688352068883042</v>
+        <v>2.812048689911286</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.673606620975107</v>
+        <v>7.822296168752935</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.73718010903935</v>
+        <v>5.909178868606013</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>245</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.253777847016671</v>
+        <v>4.22458205266404</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.030877633802234</v>
+        <v>-1.03206442024689</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.064146899810027</v>
+        <v>3.063993509805705</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.194372043398431</v>
+        <v>3.193877551020428</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.06424575560883</v>
+        <v>3.112791675374602</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.769783050550025</v>
+        <v>3.793740459499638</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.725889017814467</v>
+        <v>5.773900696804787</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.218004047497139</v>
+        <v>3.267251609890856</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.238654544035555</v>
+        <v>7.311911653815251</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.164245951787358</v>
+        <v>5.263593277081931</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.367708058833287</v>
+        <v>5.467616094851962</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.034739272413084</v>
+        <v>7.158435893441329</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.390098623181323</v>
+        <v>5.538788170959151</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.615834273407856</v>
+        <v>5.787833032974518</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>203</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2284435753769785</v>
+        <v>0.1992477810243471</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.021198369012616</v>
+        <v>5.02001158256796</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.626426984257634</v>
+        <v>4.626273594253313</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.234484640161234</v>
+        <v>6.233990147783231</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.262697550119732</v>
+        <v>1.311243469885504</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.515736604385374</v>
+        <v>4.539694013334987</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.938415407680807</v>
+        <v>3.986427086671128</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.412233463401428</v>
+        <v>7.461481025795145</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.829083819193954</v>
+        <v>8.902340928973651</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.94960837261776</v>
+        <v>10.04895569791233</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.2966313522886</v>
+        <v>6.396539388307275</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.27189620415134</v>
+        <v>10.39559282517958</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>10.83696702571474</v>
+        <v>10.98565657349257</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.07748100106442</v>
+        <v>10.24947976063108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.973</t>
+          <t>X ≈ 0.9729</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>233</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.412246502637359</v>
+        <v>-4.44144229698999</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.8435201939983941</v>
+        <v>0.8423334075537383</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.267989388181562</v>
+        <v>-1.268142778185883</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.008158502187939</v>
+        <v>1.007664009809936</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.04068439973602267</v>
+        <v>0.0892303195017945</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.378679768053793</v>
+        <v>-1.35472235910418</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.540901718173608</v>
+        <v>1.588913397163928</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.648940370524201</v>
+        <v>3.698187932917918</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.158773664645203</v>
+        <v>3.232030774424899</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.59640851638401</v>
+        <v>3.695755841678583</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.395999203617386</v>
+        <v>6.495907239636061</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.859561905328924</v>
+        <v>6.983258526357169</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.439411052015515</v>
+        <v>6.588100599793343</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6.665146702242062</v>
+        <v>6.837145461808724</v>
       </c>
     </row>
   </sheetData>
@@ -2210,209 +2210,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.03453</t>
+          <t>X &gt; 0.03462</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.014191601559574</v>
+        <v>0.01489427416156275</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.03072635694989856</v>
+        <v>0.03067399869313192</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05711335172082244</v>
+        <v>-0.05695611485742091</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01148312608676605</v>
+        <v>-0.0114397321428612</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.05119332601799442</v>
+        <v>0.04982289812011942</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.06812310663125487</v>
+        <v>0.06733147871145206</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1192936114010621</v>
+        <v>0.1177530679511634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.1067217987485805</v>
+        <v>0.1051832634907086</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2063416188655225</v>
+        <v>0.2039244843691606</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1790304878130939</v>
+        <v>0.1760227965669898</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.233338469899131</v>
+        <v>0.2301696856206306</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3061022694147013</v>
+        <v>0.3021317279395248</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2432960356104843</v>
+        <v>0.2388575796866803</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.188514879392585</v>
+        <v>0.1836295307219302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.06746</t>
+          <t>X &gt; 0.06754</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3996</v>
+        <v>4007</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2234952273415445</v>
+        <v>-0.233426082164911</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.125036255334706</v>
+        <v>-0.1360962768920189</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1819071993938977</v>
+        <v>-0.192777458477039</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1629389289186278</v>
+        <v>-0.1738759248719504</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08844603271698048</v>
+        <v>-0.1016846506477052</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.05305853407037375</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.001712762251059985</v>
+        <v>-0.0004808046747086792</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05189161691555455</v>
+        <v>-0.05399515445157022</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05085965602289377</v>
+        <v>0.04737872199848425</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.08975615586899011</v>
+        <v>0.08497732808453407</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1241522719273789</v>
+        <v>0.1192523104354493</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2726847757770301</v>
+        <v>0.2662901601168315</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2419517987773077</v>
+        <v>0.2344987905363212</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1315745034338036</v>
+        <v>0.1233581089894571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.1004</t>
+          <t>X &gt; 0.1005</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3892</v>
+        <v>3903</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3938481688186002</v>
+        <v>-0.4028321314003946</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2242742547457226</v>
+        <v>-0.235343074580399</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1696816046893659</v>
+        <v>-0.1808679410357925</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3330707122789462</v>
+        <v>-0.3438504236050335</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3191881101189509</v>
+        <v>-0.3334796994499385</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2129485036100789</v>
+        <v>-0.2141076298767146</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1041772995562624</v>
+        <v>-0.1074083485524611</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0954691098519973</v>
+        <v>-0.09881622937071199</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.06534172729819687</v>
+        <v>-0.07053774354857723</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.02841632873060007</v>
+        <v>-0.03563416920756879</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06368144176797585</v>
+        <v>0.05616119030950273</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.112525086276392</v>
+        <v>0.1031169668950582</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.06646698712079058</v>
+        <v>0.05534889360886552</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.00154937069726202</v>
+        <v>-0.01419261971545893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.1333</t>
+          <t>X &gt; 0.1334</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3767</v>
+        <v>3778</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.4703340199523467</v>
+        <v>-0.4784495557576989</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3477253043338209</v>
+        <v>-0.3587943204413619</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.5429878545681461</v>
+        <v>-0.5535527695296665</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5308607025991208</v>
+        <v>-0.5414576181674207</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.472268426335134</v>
+        <v>-0.4882303499172878</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.319418192861221</v>
+        <v>-0.3210972346905407</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.257260998948972</v>
+        <v>-0.2617394509319624</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2063267237724062</v>
+        <v>-0.2110889863899388</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1466983245773932</v>
+        <v>-0.1542500686056414</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.02736131960170241</v>
+        <v>-0.03810434538323904</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.02152714614990714</v>
+        <v>0.01057795031618269</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.04430712183994956</v>
+        <v>0.03069590855850635</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.01064110769105753</v>
+        <v>-0.005600529215278982</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1202302612459292</v>
+        <v>-0.1121680473940998</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3625</v>
+        <v>3635</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.6392447825959238</v>
+        <v>-0.6724815451283419</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4214944799358236</v>
+        <v>-0.4307374697136197</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8015049714995328</v>
+        <v>-0.8371915525836613</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.7390417622889274</v>
+        <v>-0.774930394886475</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.794772810540799</v>
+        <v>-0.837605616985492</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5100329220817841</v>
+        <v>-0.5373626572000703</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.4421861417647648</v>
+        <v>-0.4733177731154328</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.371044901743808</v>
+        <v>-0.3623859083957797</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.3342919899499108</v>
+        <v>-0.3293756303291389</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2321920392260779</v>
+        <v>-0.2313004759675152</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.09074434086969774</v>
+        <v>-0.09027061123234148</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.01426358834294916</v>
+        <v>0.01080917709629148</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1145897386498973</v>
+        <v>-0.1213900917650861</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2318786048468908</v>
+        <v>-0.2144688506399959</v>
       </c>
     </row>
     <row r="11">
@@ -2474,153 +2474,153 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3491</v>
+        <v>3502</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6258931994841319</v>
+        <v>-0.6593145583721807</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3667238763815135</v>
+        <v>-0.376399135049958</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.9460396991013695</v>
+        <v>-0.9542633655940165</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.8005215438565472</v>
+        <v>-0.8376216260228802</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.094937917860548</v>
+        <v>-1.112070447353624</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.6964492840528465</v>
+        <v>-0.7252598430158699</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6513994618998709</v>
+        <v>-0.6850182000952643</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5882905607093107</v>
+        <v>-0.6090773648128049</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4906454139338692</v>
+        <v>-0.5164176242735863</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3520893376932435</v>
+        <v>-0.3831504418036289</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2260211329006481</v>
+        <v>-0.2449228436906381</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1755997730247145</v>
+        <v>-0.1993359824322951</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2933293871980851</v>
+        <v>-0.321611369959129</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3665460748930158</v>
+        <v>-0.3706303523796208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.2321</t>
+          <t>X &gt; 0.2322</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3363</v>
+        <v>3373</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6444231395390929</v>
+        <v>-0.6462064994432026</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.07728730878336876</v>
+        <v>-0.08322676147817276</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.722795262947173</v>
+        <v>-0.7570091363681968</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5766305764458579</v>
+        <v>-0.6408266001099889</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8617232084892592</v>
+        <v>-0.9068185383791416</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.6669794919038949</v>
+        <v>-0.7525164318824906</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6466659388862936</v>
+        <v>-0.7243099618662399</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5337299497527042</v>
+        <v>-0.5977256606382113</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3112751665659985</v>
+        <v>-0.3681105920498808</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.253888037775198</v>
+        <v>-0.3033135804478064</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.003623030882714318</v>
+        <v>-0.03352037869480284</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.06414783071938501</v>
+        <v>-0.106870229007626</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.0514311397345395</v>
+        <v>-0.1001312972430668</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2251604652547812</v>
+        <v>-0.249425629755315</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.265</t>
+          <t>X &gt; 0.2651</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3233</v>
+        <v>3241</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5536881551103647</v>
+        <v>-0.5384544003644933</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1336844279132308</v>
+        <v>0.143999225550381</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.491193162780867</v>
+        <v>-0.5104547651886122</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2208458956290471</v>
+        <v>-0.2714197612439975</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7115479826953788</v>
+        <v>-0.7298332561891385</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5209734002699449</v>
+        <v>-0.5803903213973456</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5130339757189333</v>
+        <v>-0.5485394726024495</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.314619381856069</v>
+        <v>-0.366823666843338</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1423398809284677</v>
+        <v>-0.1879467539326427</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1066804217113386</v>
+        <v>0.06747227548980561</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3522473290868504</v>
+        <v>0.3258665180554772</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1876205919684537</v>
+        <v>0.1681837333728851</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.04584895300704517</v>
+        <v>0.03714519421262708</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.03772563493532033</v>
+        <v>-0.00491171071128349</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3090</v>
+        <v>3095</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2045195177800778</v>
+        <v>-0.1875311797256956</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5267609254974275</v>
+        <v>0.5372370660784895</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.02039628163062446</v>
+        <v>-0.0002612430960837742</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3121723137488743</v>
+        <v>0.2763734489598164</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1761273166970057</v>
+        <v>-0.1805863797544589</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.0403563898414987</v>
+        <v>-0.069247422123766</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.09274612855175235</v>
+        <v>-0.09761419911158242</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1691181497820864</v>
+        <v>0.1469179097333608</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.41710056668785</v>
+        <v>0.4005491107354047</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.7498499766389699</v>
+        <v>0.739135770475805</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7253462597447182</v>
+        <v>0.728731196365608</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5979121143654211</v>
+        <v>0.6254513725422512</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3719360183335638</v>
+        <v>0.4101165472709241</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2740470730908413</v>
+        <v>0.3544480473162821</v>
       </c>
     </row>
     <row r="15">
@@ -2682,101 +2682,101 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2955</v>
+        <v>2960</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.25372272706187</v>
+        <v>0.2723502324485949</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6866888254055397</v>
+        <v>0.6975343018330022</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1077210862413693</v>
+        <v>0.08604093829450221</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4406489325324401</v>
+        <v>0.4031542394135172</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1574446438156869</v>
+        <v>0.1502319046736247</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3534330702064423</v>
+        <v>0.3217345065445443</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2349275098588208</v>
+        <v>0.2273174450030737</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4963636672070919</v>
+        <v>0.4704651032557905</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7247442792194789</v>
+        <v>0.7035802726470095</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.246928009725558</v>
+        <v>1.230190584472147</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.298506774258541</v>
+        <v>1.296137915464072</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.231362083974275</v>
+        <v>1.253021735880957</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7773702831143297</v>
+        <v>0.8096908582752178</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7323783529686168</v>
+        <v>0.8078275172547222</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.3638</t>
+          <t>X &gt; 0.3639</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2812</v>
+        <v>2814</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.04039078764746762</v>
+        <v>0.06172215879517751</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6503490309311246</v>
+        <v>0.6618565832147922</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.09734824004762999</v>
+        <v>0.07456344598040943</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1920367809352115</v>
+        <v>0.1528003246753187</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.04464985754811579</v>
+        <v>0.05417618372339916</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2709506817816418</v>
+        <v>0.2559389752696077</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1862403225154736</v>
+        <v>0.1952828860441471</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.5009769381459392</v>
+        <v>0.5107001256608044</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7441719305138221</v>
+        <v>0.7578184256149143</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.265502955300001</v>
+        <v>1.283421662981745</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.345296818376937</v>
+        <v>1.398883488172935</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.37967497073226</v>
+        <v>1.457050225537827</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9950859950859936</v>
+        <v>1.08234129380687</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.936326623975404</v>
+        <v>1.067556862804963</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2694</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.01338356300188792</v>
+        <v>-0.007330957256279191</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5478384851620248</v>
+        <v>0.5432096062776353</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.04170852579674289</v>
+        <v>0.02132189570553322</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.01366395496530259</v>
+        <v>-0.03432282003710441</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1436387344901036</v>
+        <v>-0.115408695682909</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3764524443654835</v>
+        <v>0.3800113314848161</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4773397094497227</v>
+        <v>0.5048839992166876</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5670639387141989</v>
+        <v>0.5956375097053268</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8401575060221589</v>
+        <v>0.8926166630917223</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.178063505534922</v>
+        <v>1.256172126803641</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.233199021365294</v>
+        <v>1.348877690399277</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.267577173720618</v>
+        <v>1.40704442776417</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9587848950174589</v>
+        <v>1.107474442795287</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.073161970633741</v>
+        <v>1.245160730200404</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2523</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4719178973292983</v>
+        <v>0.4799871850140107</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5254167031953187</v>
+        <v>0.5422102975641394</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.328822092122401</v>
+        <v>0.3286687021180796</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.02305833361009491</v>
+        <v>0.02256384123209187</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1189344562971968</v>
+        <v>0.1674803760629686</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.495579195405135</v>
+        <v>0.519536604354748</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.609045609821095</v>
+        <v>0.6570572888114157</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8554133512900037</v>
+        <v>0.9046609136837205</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.0718786779222</v>
+        <v>1.145135787701896</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.411020523685082</v>
+        <v>1.510367848979655</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.245954720161322</v>
+        <v>1.345862756179997</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.042520744098084</v>
+        <v>1.166217365126329</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.9790880834125062</v>
+        <v>1.127777631190334</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.9670116052204918</v>
+        <v>1.139010364787154</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2404</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8052736533258766</v>
+        <v>0.8149089564929</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.6915917199958272</v>
+        <v>0.7092058924519691</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6295990374038496</v>
+        <v>0.6294456473995282</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.6350321676810609</v>
+        <v>0.6345376753030578</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.5127159922891948</v>
+        <v>0.5612619120549667</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7684926841538982</v>
+        <v>0.7924500931035112</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8917690137396406</v>
+        <v>0.9397806927299612</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.048660436508641</v>
+        <v>1.097907998902357</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.112470293297029</v>
+        <v>1.185727403076726</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.635263643389791</v>
+        <v>1.734610968684365</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.222575796277688</v>
+        <v>1.322483832296363</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.340148624173779</v>
+        <v>1.463845245202023</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.294373810793815</v>
+        <v>1.443063358571642</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.312122772168429</v>
+        <v>1.484121531735092</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.03093647166056</v>
+        <v>1.042519754060393</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.131778473416745</v>
+        <v>1.150238953055016</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.000396026326321</v>
+        <v>1.000242636322</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8672322322500676</v>
+        <v>0.8667377398720646</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.416738991709245</v>
+        <v>0.4652849114750168</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.670214865066896</v>
+        <v>0.694172274016509</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9366897560202148</v>
+        <v>0.9847014350105354</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.391482394059643</v>
+        <v>1.44072995645336</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.198805768704553</v>
+        <v>1.272062878484249</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.753627973252655</v>
+        <v>1.852975298547229</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.461130502437598</v>
+        <v>1.561038538456273</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.627203123625236</v>
+        <v>1.750899744653481</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.689931989363622</v>
+        <v>1.838621537141449</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.783973170757847</v>
+        <v>1.955971930324509</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2174</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7849533346910391</v>
+        <v>0.7772444969521004</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.243684444939078</v>
+        <v>1.242497658494422</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.216898340772815</v>
+        <v>1.216744950768494</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7031492433308131</v>
+        <v>0.70265475095281</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4868468107503077</v>
+        <v>0.5353927305160795</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4622337198702056</v>
+        <v>0.4861911288198186</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8375049613400094</v>
+        <v>0.8855166403303301</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.336397679098816</v>
+        <v>1.385645241492533</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.183419202428844</v>
+        <v>1.25667631220854</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.667447048233292</v>
+        <v>1.766794373527866</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.600740370193897</v>
+        <v>1.700648406212572</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.819111162843605</v>
+        <v>1.942807783871849</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.950938230413364</v>
+        <v>2.099627778191191</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.038679400419106</v>
+        <v>2.210678159985768</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>2069</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.168189817701517</v>
+        <v>1.161385759654074</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.393639780703417</v>
+        <v>1.392452994258761</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.240531034904386</v>
+        <v>1.240377644900065</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9357634283719278</v>
+        <v>0.9352689359939248</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5908039864410455</v>
+        <v>0.6393499062068173</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4048527381640952</v>
+        <v>0.4288101471137082</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.093462823557182</v>
+        <v>1.141474502547503</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.496379680012105</v>
+        <v>1.545627242405821</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.580395106862937</v>
+        <v>1.653652216642634</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.132119616477979</v>
+        <v>2.231466941772553</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.927418458217787</v>
+        <v>2.027326494236462</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.300124305111538</v>
+        <v>2.423820926139783</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.169968618545347</v>
+        <v>2.318658166323175</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.34737174098067</v>
+        <v>2.519370500547332</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1976</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.314630528170099</v>
+        <v>1.285434733817468</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.575914070733802</v>
+        <v>1.574727284289146</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.383571835776337</v>
+        <v>1.383418445772016</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.108938679769558</v>
+        <v>1.108444187391555</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6718637015726543</v>
+        <v>0.7204096213384261</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.5643794316125934</v>
+        <v>0.5883368405622065</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.390600246435497</v>
+        <v>1.438611925425818</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.935677351636599</v>
+        <v>1.984924914030316</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.228946207259582</v>
+        <v>2.302203317039279</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.694816884613928</v>
+        <v>2.794164209908502</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.237079289106774</v>
+        <v>2.336987325125449</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.726923028506633</v>
+        <v>2.850619649534877</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.509201324990791</v>
+        <v>2.657890872768618</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.734936975217323</v>
+        <v>2.906935734783985</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1880</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.72121162904012</v>
+        <v>1.692015834687489</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.97172766363586</v>
+        <v>1.970540877191205</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.576956278880822</v>
+        <v>1.5768028888765</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.494415465022371</v>
+        <v>1.493920972644368</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.115700380011788</v>
+        <v>1.16424629977756</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8811595160298467</v>
+        <v>0.9051169249794597</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.753895965274324</v>
+        <v>1.801907644264645</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.244274129998225</v>
+        <v>2.293521692391941</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.502440909645664</v>
+        <v>2.57569801942536</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.195075304805158</v>
+        <v>3.294422630099731</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.883991167821563</v>
+        <v>2.983899203840238</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.397092724432206</v>
+        <v>3.52078934546045</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.083324849842207</v>
+        <v>3.232014397620034</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.202677521345329</v>
+        <v>3.374676280911991</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1756</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.733206976299364</v>
+        <v>1.704011181946733</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.172134778451934</v>
+        <v>2.170947992007278</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.663468177295989</v>
+        <v>1.663314787291668</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.338112455280708</v>
+        <v>1.337617962902705</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.255403767788657</v>
+        <v>1.303949687554429</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.154144540020553</v>
+        <v>1.178101948970166</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.923648303761219</v>
+        <v>1.97165998275154</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.310793782981307</v>
+        <v>2.360041345375024</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.762340100262634</v>
+        <v>2.83559721004233</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.165268684342792</v>
+        <v>3.264616009637365</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.960567526082599</v>
+        <v>3.060475562101274</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.564421760442485</v>
+        <v>3.68811838147073</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.429008948131347</v>
+        <v>3.577698495909175</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.313058949155156</v>
+        <v>3.485057708721818</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>1638</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.158888609270285</v>
+        <v>2.129692814917654</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.684454652958593</v>
+        <v>2.683267866513937</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.167583146103432</v>
+        <v>2.167429756099111</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.809407801291307</v>
+        <v>1.808913308913304</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.576368553445917</v>
+        <v>1.624914473211689</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.629542338880761</v>
+        <v>1.653499747830374</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.399532834315444</v>
+        <v>2.447544513305765</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.092415350479875</v>
+        <v>3.141662912873592</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.519833682357586</v>
+        <v>3.593090792137282</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.318266534379369</v>
+        <v>4.417613859673942</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.808315070868872</v>
+        <v>3.908223106887547</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.270043650574621</v>
+        <v>4.393740271602866</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.460393407761828</v>
+        <v>4.609082955539655</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.258778630637927</v>
+        <v>4.430777390204589</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.7261</t>
+          <t>X &gt; 0.726</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1516</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.730165763660899</v>
+        <v>2.700969969308268</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.229797612549568</v>
+        <v>3.228610826104912</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.703100106422504</v>
+        <v>2.702946716418182</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.371583825208759</v>
+        <v>2.371089332830756</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.163109575543146</v>
+        <v>2.211655495308918</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.328557483806193</v>
+        <v>2.352514892755806</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.035403852772212</v>
+        <v>3.083415531762533</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.953559483391814</v>
+        <v>4.002807045785531</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.354318751671144</v>
+        <v>4.42757586145084</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.889624229747625</v>
+        <v>4.988971555042198</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.552996950115393</v>
+        <v>4.652904986134068</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.983153466586813</v>
+        <v>5.106850087615058</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.15667015944755</v>
+        <v>5.305359707225378</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.052590506244002</v>
+        <v>5.224589265810664</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>1391</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.443598707064496</v>
+        <v>2.414402912711864</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.773462218601679</v>
+        <v>2.772275432157024</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.306800107750306</v>
+        <v>2.306646717745984</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.508915977435002</v>
+        <v>2.508421485056999</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.54575223310998</v>
+        <v>2.594298152875751</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.058798441034057</v>
+        <v>3.08275584998367</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.692995342731223</v>
+        <v>3.741007021721543</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.951304125256499</v>
+        <v>5.000551687650216</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.177884873119048</v>
+        <v>5.251141982898744</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.550108420426866</v>
+        <v>5.64945574572144</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.026801949388997</v>
+        <v>6.150498570417241</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.253667630942594</v>
+        <v>6.402357178720422</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.97616819849479</v>
+        <v>6.148166958061452</v>
       </c>
     </row>
     <row r="29">
@@ -3413,150 +3413,150 @@
         <v>1242</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.188971248048574</v>
+        <v>2.159775453695943</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.671182900556403</v>
+        <v>2.669996114111747</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.598472707427774</v>
+        <v>2.598319317423453</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.889728446829345</v>
+        <v>2.889233954451342</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.995561276986471</v>
+        <v>3.044107196752243</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.69551179615457</v>
+        <v>3.719469205104183</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.335439118047816</v>
+        <v>4.383450797038137</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.156615240766719</v>
+        <v>5.205862803160436</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.417694275870353</v>
+        <v>5.49095138565005</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.69498965023292</v>
+        <v>5.794336975527493</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.409773194066119</v>
+        <v>5.509681230084794</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.249304325487472</v>
+        <v>6.373000946515717</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.714821749146694</v>
+        <v>6.863511296924521</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.537980909840208</v>
+        <v>6.70997966940687</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.8249</t>
+          <t>X &gt; 0.8248</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1104</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.863286868016367</v>
+        <v>2.834091073663735</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.244854398140951</v>
+        <v>3.243667611696296</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.302981564110546</v>
+        <v>3.302828174106224</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.704945838133689</v>
+        <v>3.704451345755686</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.347815705327854</v>
+        <v>3.396361625093625</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.375696767001116</v>
+        <v>4.423708445991437</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.99558464495351</v>
+        <v>5.044832207347227</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.659240169590163</v>
+        <v>5.732497279369859</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.258596735579133</v>
+        <v>6.357944060873706</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.963315867174018</v>
+        <v>6.063223903192693</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.631751990543833</v>
+        <v>6.755448611572078</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.207977948824627</v>
+        <v>7.356667496602455</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.161974468616378</v>
+        <v>7.333973228183041</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.8578</t>
+          <t>X &gt; 0.8577</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>950</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.57171554841301</v>
+        <v>2.542519754060379</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.644739981664983</v>
+        <v>2.643553195220328</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.881547544278362</v>
+        <v>2.881394154274041</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.011772687866724</v>
+        <v>3.011278195488721</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.42085155582366</v>
+        <v>3.469397475589432</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.054567857771517</v>
+        <v>4.102579536761837</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.376972898195312</v>
+        <v>5.426220460589029</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.842306531146221</v>
+        <v>5.915563640925917</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.676598261132149</v>
+        <v>6.775945586426722</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.050844471293011</v>
+        <v>6.150752507311687</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.822064728911492</v>
+        <v>6.945761349939737</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.665071770334933</v>
+        <v>7.813761318112761</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.680281104771971</v>
+        <v>7.852279864338634</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>765</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.506012074040811</v>
+        <v>1.47681627968818</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.986329248950838</v>
+        <v>1.985142462506182</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.898747406679455</v>
+        <v>2.898594016675133</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.551848367261293</v>
+        <v>3.55135387488329</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.96780718017866</v>
+        <v>2.016353099944432</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.918775981055575</v>
+        <v>2.942733390005188</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.402693072769807</v>
+        <v>4.450704751760128</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.504251879963455</v>
+        <v>5.553499442357172</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.48902135742761</v>
+        <v>6.562278467207307</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.55413524083631</v>
+        <v>6.653482566130883</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.826558265582655</v>
+        <v>5.92646630160133</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.821720731663468</v>
+        <v>7.945417352691713</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.663007786846791</v>
+        <v>7.811697334624618</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.150181345570054</v>
+        <v>8.322180105136717</v>
       </c>
     </row>
     <row r="33">
@@ -3621,150 +3621,150 @@
         <v>520</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.2113916617733409</v>
+        <v>0.1821958674207096</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.407897876401812</v>
+        <v>3.406711089957156</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.820818799339087</v>
+        <v>2.820665409334765</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.720274712158222</v>
+        <v>3.719780219780219</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.451215928293294</v>
+        <v>1.499761848059066</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.517820727159148</v>
+        <v>2.541778136108761</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>3.779264214046833</v>
+        <v>3.827275893037154</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.581426339490861</v>
+        <v>6.630673901884578</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.135828798352705</v>
+        <v>6.209085908132401</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.208986925099758</v>
+        <v>7.308334250394331</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.042747305301106</v>
+        <v>6.142655341319781</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.192510073041056</v>
+        <v>8.316206694069301</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.7338976812661</v>
+        <v>8.882587229043928</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.344248716108019</v>
+        <v>9.516247475674682</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.9566</t>
+          <t>X &gt; 0.9565</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>317</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.2004719820839469</v>
+        <v>0.1712761877313156</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.374774848010659</v>
+        <v>2.373588061566004</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.664546050006393</v>
+        <v>1.664392660002072</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.110228606843982</v>
+        <v>2.109734114465979</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.571939053748288</v>
+        <v>1.62048497351406</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.238398256884942</v>
+        <v>1.262355665834555</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3.67734720361247</v>
+        <v>3.725358882602791</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.049395279068627</v>
+        <v>6.098642841462343</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.411126056299793</v>
+        <v>4.484383166079489</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.453951739465204</v>
+        <v>5.553299064759777</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.880165407703437</v>
+        <v>5.980073443722112</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.860915799806392</v>
+        <v>6.984612420834637</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.387137186240622</v>
+        <v>7.53582673401845</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.874702489464006</v>
+        <v>9.046701249030669</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.9895</t>
+          <t>X &gt; 0.9894</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>5.867893716190927</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.497674207012629</v>
+        <v>8.521631615962242</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.70779996586449</v>
+        <v>12.75704752825821</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>6.988367866230462</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.00358937544868</v>
+        <v>15.17558813501534</v>
       </c>
     </row>
   </sheetData>
@@ -3904,209 +3904,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.03453</t>
+          <t>X &lt; 0.03462</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.1291594439345971</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.400801238277339</v>
+        <v>-6.327544128497642</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.869767653654819</v>
+        <v>-4.770420328360245</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.455421192867391</v>
+        <v>-7.355513156848716</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.99247161194064</v>
+        <v>-10.86877499091239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.841193893825476</v>
+        <v>-7.692504346047649</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.06746</t>
+          <t>X &lt; 0.06754</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>163</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.801292558422702</v>
+        <v>6.02647354096667</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4.803603397874213</v>
+        <v>5.053052553371792</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.408832013119174</v>
+        <v>4.659314565057088</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.539057156707536</v>
+        <v>4.789198606271768</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.773773738581163</v>
+        <v>3.080437270197898</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.457650835700917</v>
+        <v>2.481608244650531</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.759443543919403</v>
+        <v>1.807455222909724</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.519368765163343</v>
+        <v>2.568616327557059</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.6178958110945558</v>
+        <v>0.6911529208742522</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2320229852353037</v>
+        <v>-0.1326756599407304</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.050221076010828</v>
+        <v>-0.9503130399921531</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.696824518747533</v>
+        <v>-4.573127897719289</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.889981507030271</v>
+        <v>-3.741291959252443</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.823755059257728</v>
+        <v>-1.651756299691066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.1004</t>
+          <t>X &lt; 0.1005</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>267</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.946050261600476</v>
+        <v>6.071977727351822</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.334864168536647</v>
+        <v>4.488800642195969</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.441965442957638</v>
+        <v>2.60252534044843</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.193913432987955</v>
+        <v>5.344349680170566</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.030155715098253</v>
+        <v>5.228234867576866</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.829402403909363</v>
+        <v>3.853359812858976</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.621096539025217</v>
+        <v>2.669108218015538</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.154027895238478</v>
+        <v>2.203275457632195</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.093045738715702</v>
+        <v>2.166302848495398</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.617658777591835</v>
+        <v>1.717006102886408</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2893621137136719</v>
+        <v>0.3892701497323472</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4253234043429899</v>
+        <v>-0.3016267833147452</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2781212479615718</v>
+        <v>0.4268107957393994</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8783887333940967</v>
+        <v>1.050387492960759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.1333</t>
+          <t>X &lt; 0.1334</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>392</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.741796572059577</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.071163182524266</v>
+        <v>4.176431191738338</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.207004042667194</v>
+        <v>5.309410760675533</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.337229186255556</v>
+        <v>5.439294801890213</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.798939633159861</v>
+        <v>4.950045660938294</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.565701417896982</v>
+        <v>3.589658826846595</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.225889017814488</v>
+        <v>3.273900696804809</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.503718333211424</v>
+        <v>2.552965895605141</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.187634135872329</v>
+        <v>2.260891245652026</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6228100996496124</v>
+        <v>0.7227181356682877</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4020862111886103</v>
+        <v>0.525782832216855</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7472414803241918</v>
+        <v>0.8959310281020194</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.738283252999693</v>
+        <v>1.65517997175003</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.447922920776506</v>
+        <v>4.659348137869067</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.398534580521662</v>
+        <v>3.448610531297945</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.438220124605586</v>
+        <v>5.66194889307635</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.193913432987955</v>
+        <v>5.419393455706299</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.591953467907238</v>
+        <v>5.86124301121621</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.829402403909363</v>
+        <v>4.008483072962953</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.557426127040202</v>
+        <v>3.76125981955839</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.903091565650463</v>
+        <v>2.843829904760199</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.842109409127687</v>
+        <v>2.806857295623402</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.179456530400827</v>
+        <v>2.169944602658887</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.225691701728643</v>
+        <v>1.218140603720933</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.511006183671995</v>
+        <v>0.5286437896839544</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.401716753579549</v>
+        <v>1.441897078073396</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.001984239012074</v>
+        <v>1.877857827939231</v>
       </c>
     </row>
     <row r="11">
@@ -4171,150 +4171,150 @@
         <v>668</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.357407322759066</v>
+        <v>3.525655686290364</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.345023624904812</v>
+        <v>2.389572490851357</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.944264216197681</v>
+        <v>4.976460433982254</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.325986365774064</v>
+        <v>4.510219288907813</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.883505195911901</v>
+        <v>5.958377003395533</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.935370243511059</v>
+        <v>4.083109938634593</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.850659884244891</v>
+        <v>4.022453849409132</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.383591240458152</v>
+        <v>3.494822458858238</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.023207886330589</v>
+        <v>3.158896187539085</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.322989688803119</v>
+        <v>2.484544437815281</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.669186734135749</v>
+        <v>1.769094770154425</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.404163688886271</v>
+        <v>1.527860309914516</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.031917027189635</v>
+        <v>2.180606574967463</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.257652677416168</v>
+        <v>2.279950838180433</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.2321</t>
+          <t>X &lt; 0.2322</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.795465879013385</v>
+        <v>2.782540728039542</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6817672231354948</v>
+        <v>0.7012316379023673</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.050814933857836</v>
+        <v>3.171752678230249</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.552899373928611</v>
+        <v>2.803504714463607</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.77340379068216</v>
+        <v>3.933184589700986</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.065752694689102</v>
+        <v>3.406443396035868</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.106670476126453</v>
+        <v>3.418171888427523</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.513973691636195</v>
+        <v>2.774904671115344</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.69922269089232</v>
+        <v>1.934271235946007</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.477444598080048</v>
+        <v>1.683213756852787</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3933464548952372</v>
+        <v>0.5476355555848187</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6789808886575912</v>
+        <v>0.8567433218079259</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6357144574547391</v>
+        <v>0.8379969385314254</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.238334529791814</v>
+        <v>1.337982829405014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.265</t>
+          <t>X &lt; 0.2651</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.986252968389223</v>
+        <v>1.918916990481215</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1631462570750415</v>
+        <v>-0.1978780242370775</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.702577514251736</v>
+        <v>1.756302877522927</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8640190195193114</v>
+        <v>1.03239823143771</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.586224622505426</v>
+        <v>2.632240480537696</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.022457640299834</v>
+        <v>2.217837370991525</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.106518855956644</v>
+        <v>2.217985825502964</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.316174350100944</v>
+        <v>1.491544542497984</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8241577108195344</v>
+        <v>0.9788118903047263</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.02576108551032519</v>
+        <v>0.107846767951969</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8770139679084394</v>
+        <v>-0.7886928803510216</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3038427121048386</v>
+        <v>-0.2403470858429415</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1993362340832903</v>
+        <v>0.2256359994339263</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3784736704193605</v>
+        <v>0.2593956084891218</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6353630392330913</v>
+        <v>0.5831476395636201</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.254892821272598</v>
+        <v>-1.277037755841548</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.06826885719042508</v>
+        <v>-0.008725882660399975</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.818473318209918</v>
+        <v>-0.7098667721936494</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5985443912642125</v>
+        <v>0.6064730666002305</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2952599701156373</v>
+        <v>0.3755147048129572</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5416063495232919</v>
+        <v>0.5509226166838701</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.298596622621659</v>
+        <v>-0.2344790174852136</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9192802716817496</v>
+        <v>-0.8699065280029004</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.862482650101164</v>
+        <v>-1.829048793673948</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.787333062092692</v>
+        <v>-1.797007226595582</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.421976747328124</v>
+        <v>-1.502219066216938</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.762867236059563</v>
+        <v>-0.8741211788272665</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5783964591096549</v>
+        <v>-0.8111228284398138</v>
       </c>
     </row>
     <row r="15">
@@ -4376,101 +4376,101 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5800895842533649</v>
+        <v>-0.6217702813730241</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.447474024424629</v>
+        <v>-1.466031110371247</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2719974752953718</v>
+        <v>-0.2177329738912093</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.006772434243764</v>
+        <v>-0.9088669950739003</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3043671982575731</v>
+        <v>-0.2859975856050454</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7068354114042705</v>
+        <v>-0.6262380582232225</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3326470726780499</v>
+        <v>-0.3132749141803259</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.048265840739845</v>
+        <v>-0.9814791839093715</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.523498204387721</v>
+        <v>-1.468477665968692</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.787667207842695</v>
+        <v>-2.743074736658215</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.909518324677862</v>
+        <v>-2.903269831773024</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.747979785359263</v>
+        <v>-2.801085105040691</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.629970815382478</v>
+        <v>-1.708639725819395</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.607706305614442</v>
+        <v>-1.79017337620072</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.3638</t>
+          <t>X &lt; 0.3639</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1347</v>
+        <v>1356</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.04728771195028258</v>
+        <v>-0.09075698617731121</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.142249616223552</v>
+        <v>-1.160737590394746</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2095873726600033</v>
+        <v>-0.1615137018766077</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3345081433626405</v>
+        <v>-0.2515710096355335</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.02049183218847617</v>
+        <v>-0.04081606265824433</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4216584928078788</v>
+        <v>-0.3885844528441353</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1704399279650062</v>
+        <v>-0.1890017308819125</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8932363035655655</v>
+        <v>-0.908918858296424</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.324314685106849</v>
+        <v>-1.347516797476928</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.396291216447807</v>
+        <v>-2.426286798659703</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.561241298687492</v>
+        <v>-2.664668506534646</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.635311105039584</v>
+        <v>-2.788286158211172</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.828759246375988</v>
+        <v>-2.003503081825144</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.785041444362548</v>
+        <v>-2.049443470547239</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.05801423351439183</v>
+        <v>0.04708871347101962</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8084189820951337</v>
+        <v>-0.7958461105811878</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.08307947041284081</v>
+        <v>-0.04557333173573852</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.08402960133683024</v>
+        <v>0.1209716209716163</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3289426791543733</v>
+        <v>0.2749018024443046</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5581884639213257</v>
+        <v>-0.5614689202738248</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6741220735785873</v>
+        <v>-0.7206323390816038</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9005325581716406</v>
+        <v>-0.9474957340163215</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.332774027392986</v>
+        <v>-1.420851721805235</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.941795920373345</v>
+        <v>-2.073134517484164</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.041511759884386</v>
+        <v>-2.240815044856966</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.10650413701611</v>
+        <v>-2.349253438215484</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.534755902530726</v>
+        <v>-1.796544066201108</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.817473520699544</v>
+        <v>-2.120191965642817</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1636</v>
+        <v>1647</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6919530226507788</v>
+        <v>-0.7007028984696149</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6333642595205191</v>
+        <v>-0.6554119498498423</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5099457609336753</v>
+        <v>-0.5063272602393312</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.0175922184672217</v>
+        <v>0.01823433054573087</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1229014436964206</v>
+        <v>-0.1966335439885043</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6437925986877531</v>
+        <v>-0.6763255125084839</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7565286601513961</v>
+        <v>-0.8253145636645627</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.190755802362418</v>
+        <v>-1.258595026404315</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.462610239757268</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.974877990472471</v>
+        <v>-2.114742672682588</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.862006663342214</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.407612027081051</v>
+        <v>-1.588980598928799</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.305574148065226</v>
+        <v>-1.52630000023165</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.351632419870917</v>
+        <v>-1.608174550386686</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1755</v>
+        <v>1766</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.066888881213089</v>
+        <v>-1.075109011155973</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7814060285217792</v>
+        <v>-0.8012236314834595</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8628644483305692</v>
+        <v>-0.8573138989202889</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8155718775127312</v>
+        <v>-0.8098455598455558</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6432372375884441</v>
+        <v>-0.7055469276722448</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.939027302859607</v>
+        <v>-0.9659401884077568</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.050038152145433</v>
+        <v>-1.109163865737642</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.316293487530508</v>
+        <v>-1.375490362744699</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.346688684164782</v>
+        <v>-1.438592500415581</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.052284776478928</v>
+        <v>-2.175585784373162</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.486788005804165</v>
+        <v>-1.614443410691358</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.648893543262972</v>
+        <v>-1.808227695070983</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.582380573508736</v>
+        <v>-1.776504669436775</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.667147295287997</v>
+        <v>-1.89284739321635</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1881</v>
+        <v>1892</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.21375657963678</v>
+        <v>-1.22267094207038</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.213074125711231</v>
+        <v>-1.229389803369166</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.209917905816219</v>
+        <v>-1.202738931988648</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9986367307088031</v>
+        <v>-0.9922637824846063</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4504934734161097</v>
+        <v>-0.5065708513299256</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7066162969073062</v>
+        <v>-0.7315012161179624</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9746471288475718</v>
+        <v>-1.027100904467616</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.572236372995384</v>
+        <v>-1.622750755649669</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.286677115669661</v>
+        <v>-1.367958818358822</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.948838008587238</v>
+        <v>-2.057942932338541</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.594032051223472</v>
+        <v>-1.705934063997859</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.796153679563226</v>
+        <v>-1.935803703136465</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.868571050851941</v>
+        <v>-2.038214103801785</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.039017140842049</v>
+        <v>-2.236069974317189</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1985</v>
+        <v>1996</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8292643788826979</v>
+        <v>-0.8168847332535165</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.21278314513048</v>
+        <v>-1.204842694903398</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.33056088310272</v>
+        <v>-1.323100640260883</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.722563151732281</v>
+        <v>-0.718060105398088</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4816981987030857</v>
+        <v>-0.5321775342543731</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4079000648436235</v>
+        <v>-0.4318899124095807</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.76661159688922</v>
+        <v>-0.8149914751413547</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.357278601976518</v>
+        <v>-1.403791632580962</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.13997328900718</v>
+        <v>-1.21402945726183</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.661048268464846</v>
+        <v>-1.760896518836432</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.586876591928423</v>
+        <v>-1.687798347062873</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.826943296940762</v>
+        <v>-1.952716074853477</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.967938247155935</v>
+        <v>-2.12045579703365</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.117677267228551</v>
+        <v>-2.295067461892764</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2090</v>
+        <v>2101</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.125709183173441</v>
+        <v>-1.113992563173781</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.237677765843664</v>
+        <v>-1.230061271614062</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.226521295121422</v>
+        <v>-1.219981443812081</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8804578885743837</v>
+        <v>-0.8753806591324462</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5357192423007575</v>
+        <v>-0.5809891544928831</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3077640788832312</v>
+        <v>-0.3298890776637151</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.9388312336623486</v>
+        <v>-0.981511145351412</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.380258921812725</v>
+        <v>-1.421879856649255</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.415575644459857</v>
+        <v>-1.480847615134458</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.953271542316301</v>
+        <v>-2.041656613848311</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.749894835167126</v>
+        <v>-1.8399419093383</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.119668188468005</v>
+        <v>-2.231454156729939</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.987876957294766</v>
+        <v>-2.12524414034786</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.214455737333282</v>
+        <v>-2.373878105550375</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2183</v>
+        <v>2194</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.160333152574424</v>
+        <v>-1.128145354565277</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.290279800135771</v>
+        <v>-1.282772137604042</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.250775058034172</v>
+        <v>-1.244396512870011</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9594755421474375</v>
+        <v>-0.9542390458905956</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5609963120211319</v>
+        <v>-0.6021795605096685</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4213886257882251</v>
+        <v>-0.4409997581132714</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.120630411875197</v>
+        <v>-1.158569701622625</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.654596431707787</v>
+        <v>-1.691004419793749</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.873944791859657</v>
+        <v>-1.931065209508496</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.287953034803159</v>
+        <v>-2.366719994723603</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.873362202757171</v>
+        <v>-1.954750211707079</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.31752337177501</v>
+        <v>-2.418345638843697</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.117750670382257</v>
+        <v>-2.242347062177387</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.370927999068698</v>
+        <v>-2.515517477694651</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2279</v>
+        <v>2290</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.390165594234183</v>
+        <v>-1.359438789715469</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.494982961660156</v>
+        <v>-1.48685971803588</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.299100582589034</v>
+        <v>-1.292763534602649</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.189326390103439</v>
+        <v>-1.183229813664603</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.8739588968815326</v>
+        <v>-0.9098978702130935</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6404147845962598</v>
+        <v>-0.6571573931139767</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.313945288611492</v>
+        <v>-1.347366617260562</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.75765798974664</v>
+        <v>-1.789990799267933</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.926612263212704</v>
+        <v>-1.978026543685935</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.49037963037717</v>
+        <v>-2.560722150920128</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.233393731576129</v>
+        <v>-2.305464354074225</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.657572549290585</v>
+        <v>-2.747358885203099</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.396331738437013</v>
+        <v>-2.508139024187784</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.541699911832723</v>
+        <v>-2.672197267355216</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2403</v>
+        <v>2414</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.239194176229717</v>
+        <v>-1.212213184590325</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.462702537676861</v>
+        <v>-1.455201523398152</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.214296872064907</v>
+        <v>-1.208676382893628</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9376678425932923</v>
+        <v>-0.933050447901941</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.87337904555541</v>
+        <v>-0.9049970331752633</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7609815572424665</v>
+        <v>-0.7750928541726338</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.279784620935615</v>
+        <v>-1.309190284321225</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.600152355786463</v>
+        <v>-1.629020948719372</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.888065911588527</v>
+        <v>-1.933264713548532</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.175740312764162</v>
+        <v>-2.238812151590778</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.025543506131847</v>
+        <v>-2.089737007746123</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.467573087042119</v>
+        <v>-2.547267580001012</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.366191912999874</v>
+        <v>-2.464761074826114</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.325939190034944</v>
+        <v>-2.441881388005143</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2521</v>
+        <v>2532</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.375943654843745</v>
+        <v>-1.350976264965574</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.624672198608053</v>
+        <v>-1.616873815703215</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.406304787974072</v>
+        <v>-1.400121668314284</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.136577246629734</v>
+        <v>-1.131336405529964</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9818944395996851</v>
+        <v>-1.009319979204584</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.979533045995332</v>
+        <v>-0.9909293139215194</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.438603361415687</v>
+        <v>-1.463722985988511</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.924174707661443</v>
+        <v>-1.948007070413418</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.162027343921494</v>
+        <v>-2.200528718470807</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.674105230269618</v>
+        <v>-2.727458033032015</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.342599519031452</v>
+        <v>-2.397778583729526</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.643567246389424</v>
+        <v>-2.713026503672204</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.764912786616534</v>
+        <v>-2.850231866586064</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.676469558081109</v>
+        <v>-2.777469865436032</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.7261</t>
+          <t>X &lt; 0.726</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2643</v>
+        <v>2654</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.539650970293394</v>
+        <v>-1.516486028111586</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.738053159379724</v>
+        <v>-1.73019813734966</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.547913448066865</v>
+        <v>-1.541435903986056</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.322347573208127</v>
+        <v>-1.316602316602321</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.199613634300974</v>
+        <v>-1.222659365725278</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.25920100629412</v>
+        <v>-1.267821355308911</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.625670473906723</v>
+        <v>-1.646663921376167</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.18596048282236</v>
+        <v>-2.205358486779396</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.377998763813231</v>
+        <v>-2.410478994809715</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.679057595547704</v>
+        <v>-2.725381093704762</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.485655508815988</v>
+        <v>-2.533121271980349</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.733402388788242</v>
+        <v>-2.79361721695944</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.830747960535362</v>
+        <v>-2.90504133824566</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.811663854106484</v>
+        <v>-2.899554506819094</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2768</v>
+        <v>2779</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.204396792850069</v>
+        <v>-1.184896925173518</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.286346727914733</v>
+        <v>-1.280676943005936</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.158338063948761</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.224898904721663</v>
+        <v>-1.219817650975777</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.239914511306715</v>
+        <v>-1.25959142420669</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.463558124536704</v>
+        <v>-1.469910749100038</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.745337310554696</v>
+        <v>-1.762762209563775</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.409616863881112</v>
+        <v>-2.425050445581242</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.487642033015717</v>
+        <v>-2.514941501239839</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.669190453077618</v>
+        <v>-2.709010065368957</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.529831325018407</v>
+        <v>-2.570500661555847</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.909267211046703</v>
+        <v>-2.960519995278752</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.021248580922425</v>
+        <v>-3.0847619685211</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.920646793007144</v>
+        <v>-2.996416183084698</v>
       </c>
     </row>
     <row r="29">
@@ -5104,153 +5104,153 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2917</v>
+        <v>2928</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9109501602271877</v>
+        <v>-0.8950149190726364</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.036451730972715</v>
+        <v>-1.032064420246918</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.105725967369608</v>
+        <v>-1.101521624454854</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.196416044983515</v>
+        <v>-1.19172420499855</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.23806847151743</v>
+        <v>-1.254291214982764</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.503546794208368</v>
+        <v>-1.508211383908005</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.75521657190847</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.121631635719012</v>
+        <v>-2.134860155060522</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.198689181955842</v>
+        <v>-2.22196394893178</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.311527651046454</v>
+        <v>-2.345616846257997</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.189602536637771</v>
+        <v>-2.224402370671392</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.547798778778599</v>
+        <v>-2.591511867232889</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.743932233849634</v>
+        <v>-2.797692204734993</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.705407147397686</v>
+        <v>-2.769376736179041</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.8249</t>
+          <t>X &lt; 0.8248</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3055</v>
+        <v>3066</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.014162445136698</v>
+        <v>-0.9998812305381648</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.076125599307339</v>
+        <v>-1.071846414916131</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.192679118268416</v>
+        <v>-1.188359365045869</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.306077402285254</v>
+        <v>-1.301226082110354</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.17431128600677</v>
+        <v>-1.187855412728922</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.283819193481754</v>
+        <v>-1.287985139002593</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.481751713200318</v>
+        <v>-1.494008744876197</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.735425870696858</v>
+        <v>-1.74723074555132</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.942351191591996</v>
+        <v>-1.962206329424909</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.153738450211428</v>
+        <v>-2.182394890171935</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.046501575314679</v>
+        <v>-2.075757070641011</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.28879386999008</v>
+        <v>-2.32590543109368</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.494958541045627</v>
+        <v>-2.54050223447593</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.513361758523736</v>
+        <v>-2.567399470985968</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.8578</t>
+          <t>X &lt; 0.8577</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3209</v>
+        <v>3220</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.742865130472282</v>
+        <v>-0.7315779554159079</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6925367712231463</v>
+        <v>-0.6898235635081846</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8533331356824121</v>
+        <v>-0.8503818968100276</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.8617741802354928</v>
+        <v>-0.8586908447589607</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9794624672701175</v>
+        <v>-0.9907091241400039</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.9140077800501416</v>
+        <v>-0.9180922289660671</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.106403600725471</v>
+        <v>-1.117063931996817</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.525703699987545</v>
+        <v>-1.535309216051424</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.632229217060633</v>
+        <v>-1.648695844998201</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.874124952129762</v>
+        <v>-1.897621084593261</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.688357206625327</v>
+        <v>-1.712663401370968</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.917268812041485</v>
+        <v>-1.947962718144815</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.164736394938075</v>
+        <v>-2.202121294348238</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.202482832181651</v>
+        <v>-2.246772113431874</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3394</v>
+        <v>3405</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3235928723306571</v>
+        <v>-0.315846172458663</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.363388089540635</v>
+        <v>-0.361945626460745</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6542743894104817</v>
+        <v>-0.6521322847744031</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7726295633547551</v>
+        <v>-0.7700271909642424</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4135979237377185</v>
+        <v>-0.4234277333027521</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5999154461325844</v>
+        <v>-0.6034922103042746</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.903973747638652</v>
+        <v>-0.9121054758870173</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.178754655984257</v>
+        <v>-1.186287061514378</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.370960528824973</v>
+        <v>-1.383402248871889</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.381020771735486</v>
+        <v>-1.399441546703841</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.216372732741512</v>
+        <v>-1.23545950158379</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.66637368160243</v>
+        <v>-1.689494238400059</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.628626392598179</v>
+        <v>-1.657635906599054</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.769708040158704</v>
+        <v>-1.803644086507639</v>
       </c>
     </row>
     <row r="33">
@@ -5312,153 +5312,153 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3639</v>
+        <v>3650</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.01651296372164524</v>
+        <v>-0.01215932693448707</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4081799105058792</v>
+        <v>-0.4067788062744029</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4046817275312975</v>
+        <v>-0.4034431780625383</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5062784003910608</v>
+        <v>-0.5046838407494221</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1800256371587992</v>
+        <v>-0.1866488988873414</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3063656430924766</v>
+        <v>-0.3089810008723575</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4584673358075975</v>
+        <v>-0.4641777995650216</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.8832249214567014</v>
+        <v>-0.8878414995629882</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7921033134432989</v>
+        <v>-0.8005426302239158</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9408367620557954</v>
+        <v>-0.9526863382124588</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.7734568090908169</v>
+        <v>-0.7858965338513144</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.080882697330573</v>
+        <v>-1.095917326488461</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.15621220884379</v>
+        <v>-1.17472056860899</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.272467626082353</v>
+        <v>-1.294079183967042</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.9566</t>
+          <t>X &lt; 0.9565</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3842</v>
+        <v>3853</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.003613825605683019</v>
+        <v>-0.001058539837835326</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1222007224565047</v>
+        <v>-0.121749453380481</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.139611634488702</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1510408881293515</v>
+        <v>-0.1505676565215879</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1039745317270828</v>
+        <v>-0.1079145252827587</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.05405195972132759</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2265714675487942</v>
+        <v>-0.2301174907811046</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4456006875361709</v>
+        <v>-0.4486312190116308</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2844087493868059</v>
+        <v>-0.289996916766917</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3660160750202479</v>
+        <v>-0.3736525468374694</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.4001855745628546</v>
+        <v>-0.4077755555841449</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4813472870806237</v>
+        <v>-0.4907872199285137</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.522692722865294</v>
+        <v>-0.5342025198682947</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6727696637422227</v>
+        <v>-0.6858927147863056</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.9895</t>
+          <t>X &lt; 0.9894</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4075</v>
+        <v>4086</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.2548886332740778</v>
+        <v>-0.2534638619692018</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.0671449422916055</v>
+        <v>-0.06693459086274345</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2039562298412321</v>
+        <v>-0.2034047357995732</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.08492253857146181</v>
+        <v>-0.0846819196428612</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.09572146340413923</v>
+        <v>-0.09669724840002658</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1278112553574786</v>
+        <v>-0.1280764353090689</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1256843405832555</v>
+        <v>-0.1265665020463871</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2118275764045663</v>
+        <v>-0.2125097961378373</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08777602819330355</v>
+        <v>-0.08940233059050229</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1396750772763937</v>
+        <v>-0.1418256141909637</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01187977433823306</v>
+        <v>-0.01438888615731315</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.06181531704593368</v>
+        <v>-0.06479586501546919</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1247118152236695</v>
+        <v>-0.1281597924689422</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2532029120184589</v>
+        <v>-0.2568991036393058</v>
       </c>
     </row>
   </sheetData>
